--- a/results/excel_reports/vgg16_resnet50_random_noise.xlsx
+++ b/results/excel_reports/vgg16_resnet50_random_noise.xlsx
@@ -199,12 +199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$2:$U$2</f>
+              <f>'Data'!$B$2:$V$2</f>
             </numRef>
           </val>
         </ser>
@@ -231,12 +231,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$3:$U$3</f>
+              <f>'Data'!$B$3:$V$3</f>
             </numRef>
           </val>
         </ser>
@@ -263,12 +263,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$4:$U$4</f>
+              <f>'Data'!$B$4:$V$4</f>
             </numRef>
           </val>
         </ser>
@@ -295,12 +295,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$5:$U$5</f>
+              <f>'Data'!$B$5:$V$5</f>
             </numRef>
           </val>
         </ser>
@@ -327,12 +327,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$6:$U$6</f>
+              <f>'Data'!$B$6:$V$6</f>
             </numRef>
           </val>
         </ser>
@@ -359,12 +359,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$7:$U$7</f>
+              <f>'Data'!$B$7:$V$7</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$8:$U$8</f>
+              <f>'Data'!$B$8:$V$8</f>
             </numRef>
           </val>
         </ser>
@@ -423,12 +423,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$9:$U$9</f>
+              <f>'Data'!$B$9:$V$9</f>
             </numRef>
           </val>
         </ser>
@@ -455,12 +455,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$10:$U$10</f>
+              <f>'Data'!$B$10:$V$10</f>
             </numRef>
           </val>
         </ser>
@@ -487,12 +487,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$11:$U$11</f>
+              <f>'Data'!$B$11:$V$11</f>
             </numRef>
           </val>
         </ser>
@@ -519,12 +519,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$12:$U$12</f>
+              <f>'Data'!$B$12:$V$12</f>
             </numRef>
           </val>
         </ser>
@@ -551,12 +551,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$13:$U$13</f>
+              <f>'Data'!$B$13:$V$13</f>
             </numRef>
           </val>
         </ser>
@@ -583,12 +583,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$14:$U$14</f>
+              <f>'Data'!$B$14:$V$14</f>
             </numRef>
           </val>
         </ser>
@@ -975,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -999,6 +999,7 @@
     <col width="7" customWidth="1" min="19" max="19"/>
     <col width="7" customWidth="1" min="20" max="20"/>
     <col width="7" customWidth="1" min="21" max="21"/>
+    <col width="7" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1067,6 +1068,9 @@
       <c r="U1" s="1" t="n">
         <v>95</v>
       </c>
+      <c r="V1" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1134,6 +1138,9 @@
       <c r="U2" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1201,6 +1208,9 @@
       <c r="U3" t="n">
         <v>0.049</v>
       </c>
+      <c r="V3" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1268,6 +1278,9 @@
       <c r="U4" t="n">
         <v>0.032</v>
       </c>
+      <c r="V4" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1335,6 +1348,9 @@
       <c r="U5" t="n">
         <v>0.022</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1402,6 +1418,9 @@
       <c r="U6" t="n">
         <v>0.007</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1469,6 +1488,9 @@
       <c r="U7" t="n">
         <v>0.034</v>
       </c>
+      <c r="V7" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1536,6 +1558,9 @@
       <c r="U8" t="n">
         <v>0.017</v>
       </c>
+      <c r="V8" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1603,6 +1628,9 @@
       <c r="U9" t="n">
         <v>0.532</v>
       </c>
+      <c r="V9" t="n">
+        <v>0.526</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1670,6 +1698,9 @@
       <c r="U10" t="n">
         <v>0.012</v>
       </c>
+      <c r="V10" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1737,6 +1768,9 @@
       <c r="U11" t="n">
         <v>0.026</v>
       </c>
+      <c r="V11" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1804,6 +1838,9 @@
       <c r="U12" t="n">
         <v>0.002</v>
       </c>
+      <c r="V12" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1871,6 +1908,9 @@
       <c r="U13" t="n">
         <v>0.227</v>
       </c>
+      <c r="V13" t="n">
+        <v>0.226</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1938,6 +1978,9 @@
       <c r="U14" t="n">
         <v>0.019</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/excel_reports/vgg16_resnet50_random_noise.xlsx
+++ b/results/excel_reports/vgg16_resnet50_random_noise.xlsx
@@ -1572,64 +1572,64 @@
         <v>0.86</v>
       </c>
       <c r="C9" t="n">
-        <v>0.845</v>
+        <v>0.786</v>
       </c>
       <c r="D9" t="n">
-        <v>0.834</v>
+        <v>0.728</v>
       </c>
       <c r="E9" t="n">
-        <v>0.819</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.636</v>
       </c>
       <c r="G9" t="n">
-        <v>0.798</v>
+        <v>0.598</v>
       </c>
       <c r="H9" t="n">
-        <v>0.787</v>
+        <v>0.551</v>
       </c>
       <c r="I9" t="n">
-        <v>0.765</v>
+        <v>0.51</v>
       </c>
       <c r="J9" t="n">
-        <v>0.757</v>
+        <v>0.457</v>
       </c>
       <c r="K9" t="n">
-        <v>0.737</v>
+        <v>0.414</v>
       </c>
       <c r="L9" t="n">
-        <v>0.721</v>
+        <v>0.377</v>
       </c>
       <c r="M9" t="n">
-        <v>0.712</v>
+        <v>0.325</v>
       </c>
       <c r="N9" t="n">
-        <v>0.68</v>
+        <v>0.267</v>
       </c>
       <c r="O9" t="n">
-        <v>0.664</v>
+        <v>0.223</v>
       </c>
       <c r="P9" t="n">
-        <v>0.632</v>
+        <v>0.169</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.606</v>
+        <v>0.121</v>
       </c>
       <c r="R9" t="n">
-        <v>0.583</v>
+        <v>0.089</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.049</v>
       </c>
       <c r="T9" t="n">
-        <v>0.549</v>
+        <v>0.023</v>
       </c>
       <c r="U9" t="n">
-        <v>0.532</v>
+        <v>0.007</v>
       </c>
       <c r="V9" t="n">
-        <v>0.526</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="10">
@@ -1852,64 +1852,64 @@
         <v>0.86</v>
       </c>
       <c r="C13" t="n">
-        <v>0.756</v>
+        <v>0.743</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.671</v>
       </c>
       <c r="E13" t="n">
-        <v>0.64</v>
+        <v>0.618</v>
       </c>
       <c r="F13" t="n">
-        <v>0.616</v>
+        <v>0.574</v>
       </c>
       <c r="G13" t="n">
-        <v>0.577</v>
+        <v>0.521</v>
       </c>
       <c r="H13" t="n">
-        <v>0.545</v>
+        <v>0.488</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="J13" t="n">
-        <v>0.463</v>
+        <v>0.386</v>
       </c>
       <c r="K13" t="n">
-        <v>0.431</v>
+        <v>0.355</v>
       </c>
       <c r="L13" t="n">
-        <v>0.407</v>
+        <v>0.309</v>
       </c>
       <c r="M13" t="n">
-        <v>0.38</v>
+        <v>0.266</v>
       </c>
       <c r="N13" t="n">
-        <v>0.355</v>
+        <v>0.227</v>
       </c>
       <c r="O13" t="n">
-        <v>0.331</v>
+        <v>0.194</v>
       </c>
       <c r="P13" t="n">
-        <v>0.297</v>
+        <v>0.131</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.271</v>
+        <v>0.095</v>
       </c>
       <c r="R13" t="n">
-        <v>0.249</v>
+        <v>0.064</v>
       </c>
       <c r="S13" t="n">
-        <v>0.238</v>
+        <v>0.03</v>
       </c>
       <c r="T13" t="n">
-        <v>0.231</v>
+        <v>0.016</v>
       </c>
       <c r="U13" t="n">
-        <v>0.227</v>
+        <v>0.003</v>
       </c>
       <c r="V13" t="n">
-        <v>0.226</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="14">

--- a/results/excel_reports/vgg16_resnet50_random_noise.xlsx
+++ b/results/excel_reports/vgg16_resnet50_random_noise.xlsx
@@ -592,6 +592,70 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="13"/>
+          <order val="13"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="14"/>
+          <order val="14"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$16:$V$16</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -665,7 +729,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -975,7 +1039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1775,138 +1839,138 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>pca1</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.86</v>
       </c>
       <c r="C12" t="n">
-        <v>0.618</v>
+        <v>0.84</v>
       </c>
       <c r="D12" t="n">
-        <v>0.545</v>
+        <v>0.827</v>
       </c>
       <c r="E12" t="n">
-        <v>0.459</v>
+        <v>0.805</v>
       </c>
       <c r="F12" t="n">
-        <v>0.398</v>
+        <v>0.777</v>
       </c>
       <c r="G12" t="n">
-        <v>0.328</v>
+        <v>0.778</v>
       </c>
       <c r="H12" t="n">
-        <v>0.273</v>
+        <v>0.74</v>
       </c>
       <c r="I12" t="n">
-        <v>0.22</v>
+        <v>0.717</v>
       </c>
       <c r="J12" t="n">
-        <v>0.169</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.134</v>
+        <v>0.64</v>
       </c>
       <c r="L12" t="n">
-        <v>0.101</v>
+        <v>0.595</v>
       </c>
       <c r="M12" t="n">
-        <v>0.076</v>
+        <v>0.555</v>
       </c>
       <c r="N12" t="n">
-        <v>0.055</v>
+        <v>0.526</v>
       </c>
       <c r="O12" t="n">
-        <v>0.035</v>
+        <v>0.461</v>
       </c>
       <c r="P12" t="n">
-        <v>0.027</v>
+        <v>0.392</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.017</v>
+        <v>0.306</v>
       </c>
       <c r="R12" t="n">
-        <v>0.008</v>
+        <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>0.003</v>
+        <v>0.148</v>
       </c>
       <c r="T12" t="n">
-        <v>0.003</v>
+        <v>0.065</v>
       </c>
       <c r="U12" t="n">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>random_baseline</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.86</v>
       </c>
       <c r="C13" t="n">
-        <v>0.743</v>
+        <v>0.618</v>
       </c>
       <c r="D13" t="n">
-        <v>0.671</v>
+        <v>0.545</v>
       </c>
       <c r="E13" t="n">
-        <v>0.618</v>
+        <v>0.459</v>
       </c>
       <c r="F13" t="n">
-        <v>0.574</v>
+        <v>0.398</v>
       </c>
       <c r="G13" t="n">
-        <v>0.521</v>
+        <v>0.328</v>
       </c>
       <c r="H13" t="n">
-        <v>0.488</v>
+        <v>0.273</v>
       </c>
       <c r="I13" t="n">
-        <v>0.43</v>
+        <v>0.22</v>
       </c>
       <c r="J13" t="n">
-        <v>0.386</v>
+        <v>0.169</v>
       </c>
       <c r="K13" t="n">
-        <v>0.355</v>
+        <v>0.134</v>
       </c>
       <c r="L13" t="n">
-        <v>0.309</v>
+        <v>0.101</v>
       </c>
       <c r="M13" t="n">
-        <v>0.266</v>
+        <v>0.076</v>
       </c>
       <c r="N13" t="n">
-        <v>0.227</v>
+        <v>0.055</v>
       </c>
       <c r="O13" t="n">
-        <v>0.194</v>
+        <v>0.035</v>
       </c>
       <c r="P13" t="n">
-        <v>0.131</v>
+        <v>0.027</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.095</v>
+        <v>0.017</v>
       </c>
       <c r="R13" t="n">
-        <v>0.064</v>
+        <v>0.008</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03</v>
+        <v>0.003</v>
       </c>
       <c r="T13" t="n">
-        <v>0.016</v>
+        <v>0.003</v>
       </c>
       <c r="U13" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="V13" t="n">
         <v>0.001</v>
@@ -1915,70 +1979,210 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>saliency</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sumDino</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>xrai</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B16" t="n">
         <v>0.86</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C16" t="n">
         <v>0.841</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D16" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E16" t="n">
         <v>0.781</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F16" t="n">
         <v>0.763</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G16" t="n">
         <v>0.73</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H16" t="n">
         <v>0.698</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I16" t="n">
         <v>0.656</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J16" t="n">
         <v>0.603</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K16" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L16" t="n">
         <v>0.504</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M16" t="n">
         <v>0.455</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N16" t="n">
         <v>0.398</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O16" t="n">
         <v>0.35</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P16" t="n">
         <v>0.293</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q16" t="n">
         <v>0.225</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R16" t="n">
         <v>0.155</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S16" t="n">
         <v>0.103</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T16" t="n">
         <v>0.059</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U16" t="n">
         <v>0.019</v>
       </c>
-      <c r="V14" t="n">
+      <c r="V16" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results/excel_reports/vgg16_resnet50_random_noise.xlsx
+++ b/results/excel_reports/vgg16_resnet50_random_noise.xlsx
@@ -656,6 +656,166 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="15"/>
+          <order val="15"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$17:$V$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="16"/>
+          <order val="16"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A18</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$18:$V$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="17"/>
+          <order val="17"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$19:$V$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="18"/>
+          <order val="18"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$20:$V$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="19"/>
+          <order val="19"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$21:$V$21</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -729,7 +889,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1039,7 +1199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1209,980 +1369,1330 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.86</v>
       </c>
       <c r="C3" t="n">
-        <v>0.821</v>
+        <v>0.836</v>
       </c>
       <c r="D3" t="n">
-        <v>0.798</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.775</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.756</v>
+        <v>0.782</v>
       </c>
       <c r="G3" t="n">
-        <v>0.732</v>
+        <v>0.776</v>
       </c>
       <c r="H3" t="n">
-        <v>0.705</v>
+        <v>0.759</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.735</v>
       </c>
       <c r="J3" t="n">
-        <v>0.635</v>
+        <v>0.699</v>
       </c>
       <c r="K3" t="n">
-        <v>0.614</v>
+        <v>0.666</v>
       </c>
       <c r="L3" t="n">
-        <v>0.571</v>
+        <v>0.633</v>
       </c>
       <c r="M3" t="n">
-        <v>0.524</v>
+        <v>0.585</v>
       </c>
       <c r="N3" t="n">
-        <v>0.486</v>
+        <v>0.533</v>
       </c>
       <c r="O3" t="n">
-        <v>0.435</v>
+        <v>0.488</v>
       </c>
       <c r="P3" t="n">
-        <v>0.374</v>
+        <v>0.414</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.322</v>
+        <v>0.338</v>
       </c>
       <c r="R3" t="n">
-        <v>0.258</v>
+        <v>0.274</v>
       </c>
       <c r="S3" t="n">
-        <v>0.186</v>
+        <v>0.187</v>
       </c>
       <c r="T3" t="n">
-        <v>0.12</v>
+        <v>0.098</v>
       </c>
       <c r="U3" t="n">
-        <v>0.049</v>
+        <v>0.03</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dinov2_pca_gaussian</t>
+          <t>dinov2_ENT</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.86</v>
       </c>
       <c r="C4" t="n">
-        <v>0.855</v>
+        <v>0.827</v>
       </c>
       <c r="D4" t="n">
-        <v>0.828</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="F4" t="n">
-        <v>0.794</v>
+        <v>0.787</v>
       </c>
       <c r="G4" t="n">
-        <v>0.772</v>
+        <v>0.769</v>
       </c>
       <c r="H4" t="n">
-        <v>0.745</v>
+        <v>0.75</v>
       </c>
       <c r="I4" t="n">
-        <v>0.717</v>
+        <v>0.719</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="K4" t="n">
-        <v>0.645</v>
+        <v>0.666</v>
       </c>
       <c r="L4" t="n">
-        <v>0.612</v>
+        <v>0.619</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.578</v>
       </c>
       <c r="N4" t="n">
-        <v>0.533</v>
+        <v>0.528</v>
       </c>
       <c r="O4" t="n">
-        <v>0.471</v>
+        <v>0.491</v>
       </c>
       <c r="P4" t="n">
-        <v>0.399</v>
+        <v>0.415</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.333</v>
+        <v>0.355</v>
       </c>
       <c r="R4" t="n">
-        <v>0.248</v>
+        <v>0.281</v>
       </c>
       <c r="S4" t="n">
-        <v>0.177</v>
+        <v>0.207</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09</v>
+        <v>0.123</v>
       </c>
       <c r="U4" t="n">
-        <v>0.032</v>
+        <v>0.051</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.86</v>
       </c>
       <c r="C5" t="n">
-        <v>0.795</v>
+        <v>0.833</v>
       </c>
       <c r="D5" t="n">
-        <v>0.751</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.802</v>
       </c>
       <c r="F5" t="n">
-        <v>0.641</v>
+        <v>0.789</v>
       </c>
       <c r="G5" t="n">
-        <v>0.606</v>
+        <v>0.781</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.506</v>
+        <v>0.727</v>
       </c>
       <c r="J5" t="n">
-        <v>0.47</v>
+        <v>0.703</v>
       </c>
       <c r="K5" t="n">
-        <v>0.423</v>
+        <v>0.656</v>
       </c>
       <c r="L5" t="n">
-        <v>0.391</v>
+        <v>0.615</v>
       </c>
       <c r="M5" t="n">
-        <v>0.329</v>
+        <v>0.576</v>
       </c>
       <c r="N5" t="n">
-        <v>0.306</v>
+        <v>0.521</v>
       </c>
       <c r="O5" t="n">
-        <v>0.28</v>
+        <v>0.465</v>
       </c>
       <c r="P5" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.243</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.153</v>
-      </c>
       <c r="S5" t="n">
-        <v>0.117</v>
+        <v>0.142</v>
       </c>
       <c r="T5" t="n">
-        <v>0.065</v>
+        <v>0.063</v>
       </c>
       <c r="U5" t="n">
-        <v>0.022</v>
+        <v>0.018</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>dinov2_PC_EV</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.86</v>
       </c>
       <c r="C6" t="n">
-        <v>0.786</v>
+        <v>0.832</v>
       </c>
       <c r="D6" t="n">
-        <v>0.739</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.804</v>
       </c>
       <c r="F6" t="n">
-        <v>0.657</v>
+        <v>0.79</v>
       </c>
       <c r="G6" t="n">
-        <v>0.629</v>
+        <v>0.781</v>
       </c>
       <c r="H6" t="n">
-        <v>0.599</v>
+        <v>0.768</v>
       </c>
       <c r="I6" t="n">
-        <v>0.556</v>
+        <v>0.73</v>
       </c>
       <c r="J6" t="n">
-        <v>0.496</v>
+        <v>0.698</v>
       </c>
       <c r="K6" t="n">
-        <v>0.467</v>
+        <v>0.658</v>
       </c>
       <c r="L6" t="n">
-        <v>0.422</v>
+        <v>0.618</v>
       </c>
       <c r="M6" t="n">
-        <v>0.368</v>
+        <v>0.569</v>
       </c>
       <c r="N6" t="n">
-        <v>0.333</v>
+        <v>0.528</v>
       </c>
       <c r="O6" t="n">
-        <v>0.266</v>
+        <v>0.464</v>
       </c>
       <c r="P6" t="n">
-        <v>0.233</v>
+        <v>0.389</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.186</v>
+        <v>0.324</v>
       </c>
       <c r="R6" t="n">
-        <v>0.122</v>
+        <v>0.24</v>
       </c>
       <c r="S6" t="n">
-        <v>0.079</v>
+        <v>0.136</v>
       </c>
       <c r="T6" t="n">
-        <v>0.037</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.007</v>
+        <v>0.019</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>dinov2_PC_L2</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.86</v>
       </c>
       <c r="C7" t="n">
-        <v>0.772</v>
+        <v>0.791</v>
       </c>
       <c r="D7" t="n">
-        <v>0.734</v>
+        <v>0.755</v>
       </c>
       <c r="E7" t="n">
-        <v>0.702</v>
+        <v>0.723</v>
       </c>
       <c r="F7" t="n">
-        <v>0.666</v>
+        <v>0.677</v>
       </c>
       <c r="G7" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H7" t="n">
-        <v>0.608</v>
+        <v>0.572</v>
       </c>
       <c r="I7" t="n">
-        <v>0.574</v>
+        <v>0.523</v>
       </c>
       <c r="J7" t="n">
-        <v>0.543</v>
+        <v>0.464</v>
       </c>
       <c r="K7" t="n">
-        <v>0.525</v>
+        <v>0.41</v>
       </c>
       <c r="L7" t="n">
-        <v>0.484</v>
+        <v>0.357</v>
       </c>
       <c r="M7" t="n">
-        <v>0.46</v>
+        <v>0.317</v>
       </c>
       <c r="N7" t="n">
-        <v>0.417</v>
+        <v>0.278</v>
       </c>
       <c r="O7" t="n">
-        <v>0.377</v>
+        <v>0.247</v>
       </c>
       <c r="P7" t="n">
-        <v>0.322</v>
+        <v>0.215</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.288</v>
+        <v>0.195</v>
       </c>
       <c r="R7" t="n">
-        <v>0.229</v>
+        <v>0.152</v>
       </c>
       <c r="S7" t="n">
-        <v>0.165</v>
+        <v>0.106</v>
       </c>
       <c r="T7" t="n">
-        <v>0.103</v>
+        <v>0.053</v>
       </c>
       <c r="U7" t="n">
-        <v>0.034</v>
+        <v>0.021</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.86</v>
       </c>
       <c r="C8" t="n">
-        <v>0.788</v>
+        <v>0.821</v>
       </c>
       <c r="D8" t="n">
-        <v>0.749</v>
+        <v>0.798</v>
       </c>
       <c r="E8" t="n">
-        <v>0.657</v>
+        <v>0.775</v>
       </c>
       <c r="F8" t="n">
-        <v>0.62</v>
+        <v>0.756</v>
       </c>
       <c r="G8" t="n">
-        <v>0.574</v>
+        <v>0.732</v>
       </c>
       <c r="H8" t="n">
-        <v>0.543</v>
+        <v>0.705</v>
       </c>
       <c r="I8" t="n">
-        <v>0.504</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.451</v>
+        <v>0.635</v>
       </c>
       <c r="K8" t="n">
-        <v>0.397</v>
+        <v>0.614</v>
       </c>
       <c r="L8" t="n">
-        <v>0.347</v>
+        <v>0.571</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3</v>
+        <v>0.524</v>
       </c>
       <c r="N8" t="n">
-        <v>0.264</v>
+        <v>0.486</v>
       </c>
       <c r="O8" t="n">
-        <v>0.234</v>
+        <v>0.435</v>
       </c>
       <c r="P8" t="n">
-        <v>0.195</v>
+        <v>0.374</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.148</v>
+        <v>0.322</v>
       </c>
       <c r="R8" t="n">
-        <v>0.114</v>
+        <v>0.258</v>
       </c>
       <c r="S8" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.186</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="U8" t="n">
-        <v>0.017</v>
+        <v>0.049</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>dinov2_pca_gaussian</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.86</v>
       </c>
       <c r="C9" t="n">
-        <v>0.786</v>
+        <v>0.855</v>
       </c>
       <c r="D9" t="n">
-        <v>0.728</v>
+        <v>0.828</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.636</v>
+        <v>0.794</v>
       </c>
       <c r="G9" t="n">
-        <v>0.598</v>
+        <v>0.772</v>
       </c>
       <c r="H9" t="n">
-        <v>0.551</v>
+        <v>0.745</v>
       </c>
       <c r="I9" t="n">
-        <v>0.51</v>
+        <v>0.717</v>
       </c>
       <c r="J9" t="n">
-        <v>0.457</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.414</v>
+        <v>0.645</v>
       </c>
       <c r="L9" t="n">
-        <v>0.377</v>
+        <v>0.612</v>
       </c>
       <c r="M9" t="n">
-        <v>0.325</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.267</v>
+        <v>0.533</v>
       </c>
       <c r="O9" t="n">
-        <v>0.223</v>
+        <v>0.471</v>
       </c>
       <c r="P9" t="n">
-        <v>0.169</v>
+        <v>0.399</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.121</v>
+        <v>0.333</v>
       </c>
       <c r="R9" t="n">
-        <v>0.089</v>
+        <v>0.248</v>
       </c>
       <c r="S9" t="n">
-        <v>0.049</v>
+        <v>0.177</v>
       </c>
       <c r="T9" t="n">
-        <v>0.023</v>
+        <v>0.09</v>
       </c>
       <c r="U9" t="n">
-        <v>0.007</v>
+        <v>0.032</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.86</v>
       </c>
       <c r="C10" t="n">
-        <v>0.783</v>
+        <v>0.795</v>
       </c>
       <c r="D10" t="n">
-        <v>0.734</v>
+        <v>0.751</v>
       </c>
       <c r="E10" t="n">
-        <v>0.705</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.657</v>
+        <v>0.641</v>
       </c>
       <c r="G10" t="n">
-        <v>0.635</v>
+        <v>0.606</v>
       </c>
       <c r="H10" t="n">
-        <v>0.591</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.506</v>
       </c>
       <c r="J10" t="n">
-        <v>0.516</v>
+        <v>0.47</v>
       </c>
       <c r="K10" t="n">
-        <v>0.463</v>
+        <v>0.423</v>
       </c>
       <c r="L10" t="n">
-        <v>0.434</v>
+        <v>0.391</v>
       </c>
       <c r="M10" t="n">
-        <v>0.373</v>
+        <v>0.329</v>
       </c>
       <c r="N10" t="n">
-        <v>0.318</v>
+        <v>0.306</v>
       </c>
       <c r="O10" t="n">
-        <v>0.286</v>
+        <v>0.28</v>
       </c>
       <c r="P10" t="n">
-        <v>0.231</v>
+        <v>0.243</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.186</v>
+        <v>0.185</v>
       </c>
       <c r="R10" t="n">
-        <v>0.129</v>
+        <v>0.153</v>
       </c>
       <c r="S10" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.117</v>
       </c>
       <c r="T10" t="n">
-        <v>0.046</v>
+        <v>0.065</v>
       </c>
       <c r="U10" t="n">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
       <c r="V10" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.86</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.786</v>
       </c>
       <c r="D11" t="n">
-        <v>0.771</v>
+        <v>0.739</v>
       </c>
       <c r="E11" t="n">
-        <v>0.724</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.657</v>
       </c>
       <c r="G11" t="n">
-        <v>0.641</v>
+        <v>0.629</v>
       </c>
       <c r="H11" t="n">
-        <v>0.612</v>
+        <v>0.599</v>
       </c>
       <c r="I11" t="n">
-        <v>0.547</v>
+        <v>0.556</v>
       </c>
       <c r="J11" t="n">
-        <v>0.509</v>
+        <v>0.496</v>
       </c>
       <c r="K11" t="n">
-        <v>0.455</v>
+        <v>0.467</v>
       </c>
       <c r="L11" t="n">
-        <v>0.417</v>
+        <v>0.422</v>
       </c>
       <c r="M11" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="N11" t="n">
-        <v>0.331</v>
+        <v>0.333</v>
       </c>
       <c r="O11" t="n">
-        <v>0.298</v>
+        <v>0.266</v>
       </c>
       <c r="P11" t="n">
-        <v>0.263</v>
+        <v>0.233</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.217</v>
+        <v>0.186</v>
       </c>
       <c r="R11" t="n">
-        <v>0.161</v>
+        <v>0.122</v>
       </c>
       <c r="S11" t="n">
-        <v>0.139</v>
+        <v>0.079</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.037</v>
       </c>
       <c r="U11" t="n">
-        <v>0.026</v>
+        <v>0.007</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pca1</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.86</v>
       </c>
       <c r="C12" t="n">
-        <v>0.84</v>
+        <v>0.772</v>
       </c>
       <c r="D12" t="n">
-        <v>0.827</v>
+        <v>0.734</v>
       </c>
       <c r="E12" t="n">
-        <v>0.805</v>
+        <v>0.702</v>
       </c>
       <c r="F12" t="n">
-        <v>0.777</v>
+        <v>0.666</v>
       </c>
       <c r="G12" t="n">
-        <v>0.778</v>
+        <v>0.64</v>
       </c>
       <c r="H12" t="n">
-        <v>0.74</v>
+        <v>0.608</v>
       </c>
       <c r="I12" t="n">
-        <v>0.717</v>
+        <v>0.574</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.543</v>
       </c>
       <c r="K12" t="n">
-        <v>0.64</v>
+        <v>0.525</v>
       </c>
       <c r="L12" t="n">
-        <v>0.595</v>
+        <v>0.484</v>
       </c>
       <c r="M12" t="n">
-        <v>0.555</v>
+        <v>0.46</v>
       </c>
       <c r="N12" t="n">
-        <v>0.526</v>
+        <v>0.417</v>
       </c>
       <c r="O12" t="n">
-        <v>0.461</v>
+        <v>0.377</v>
       </c>
       <c r="P12" t="n">
-        <v>0.392</v>
+        <v>0.322</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.306</v>
+        <v>0.288</v>
       </c>
       <c r="R12" t="n">
-        <v>0.232</v>
+        <v>0.229</v>
       </c>
       <c r="S12" t="n">
-        <v>0.148</v>
+        <v>0.165</v>
       </c>
       <c r="T12" t="n">
-        <v>0.065</v>
+        <v>0.103</v>
       </c>
       <c r="U12" t="n">
-        <v>0.019</v>
+        <v>0.034</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.86</v>
       </c>
       <c r="C13" t="n">
-        <v>0.618</v>
+        <v>0.788</v>
       </c>
       <c r="D13" t="n">
-        <v>0.545</v>
+        <v>0.749</v>
       </c>
       <c r="E13" t="n">
-        <v>0.459</v>
+        <v>0.657</v>
       </c>
       <c r="F13" t="n">
-        <v>0.398</v>
+        <v>0.62</v>
       </c>
       <c r="G13" t="n">
-        <v>0.328</v>
+        <v>0.574</v>
       </c>
       <c r="H13" t="n">
-        <v>0.273</v>
+        <v>0.543</v>
       </c>
       <c r="I13" t="n">
-        <v>0.22</v>
+        <v>0.504</v>
       </c>
       <c r="J13" t="n">
-        <v>0.169</v>
+        <v>0.451</v>
       </c>
       <c r="K13" t="n">
-        <v>0.134</v>
+        <v>0.397</v>
       </c>
       <c r="L13" t="n">
-        <v>0.101</v>
+        <v>0.347</v>
       </c>
       <c r="M13" t="n">
-        <v>0.076</v>
+        <v>0.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.055</v>
+        <v>0.264</v>
       </c>
       <c r="O13" t="n">
-        <v>0.035</v>
+        <v>0.234</v>
       </c>
       <c r="P13" t="n">
-        <v>0.027</v>
+        <v>0.195</v>
       </c>
       <c r="Q13" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U13" t="n">
         <v>0.017</v>
       </c>
-      <c r="R13" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>0.002</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.86</v>
       </c>
       <c r="C14" t="n">
-        <v>0.743</v>
+        <v>0.786</v>
       </c>
       <c r="D14" t="n">
-        <v>0.671</v>
+        <v>0.728</v>
       </c>
       <c r="E14" t="n">
-        <v>0.618</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.574</v>
+        <v>0.636</v>
       </c>
       <c r="G14" t="n">
-        <v>0.521</v>
+        <v>0.598</v>
       </c>
       <c r="H14" t="n">
-        <v>0.488</v>
+        <v>0.551</v>
       </c>
       <c r="I14" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="J14" t="n">
-        <v>0.386</v>
+        <v>0.457</v>
       </c>
       <c r="K14" t="n">
-        <v>0.355</v>
+        <v>0.414</v>
       </c>
       <c r="L14" t="n">
-        <v>0.309</v>
+        <v>0.377</v>
       </c>
       <c r="M14" t="n">
-        <v>0.266</v>
+        <v>0.325</v>
       </c>
       <c r="N14" t="n">
-        <v>0.227</v>
+        <v>0.267</v>
       </c>
       <c r="O14" t="n">
-        <v>0.194</v>
+        <v>0.223</v>
       </c>
       <c r="P14" t="n">
-        <v>0.131</v>
+        <v>0.169</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.095</v>
+        <v>0.121</v>
       </c>
       <c r="R14" t="n">
-        <v>0.064</v>
+        <v>0.089</v>
       </c>
       <c r="S14" t="n">
-        <v>0.03</v>
+        <v>0.049</v>
       </c>
       <c r="T14" t="n">
-        <v>0.016</v>
+        <v>0.023</v>
       </c>
       <c r="U14" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="V14" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sumDino</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0.86</v>
       </c>
       <c r="C15" t="n">
-        <v>0.844</v>
+        <v>0.783</v>
       </c>
       <c r="D15" t="n">
-        <v>0.832</v>
+        <v>0.734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.823</v>
+        <v>0.705</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.657</v>
       </c>
       <c r="G15" t="n">
-        <v>0.79</v>
+        <v>0.635</v>
       </c>
       <c r="H15" t="n">
-        <v>0.772</v>
+        <v>0.591</v>
       </c>
       <c r="I15" t="n">
-        <v>0.748</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.715</v>
+        <v>0.516</v>
       </c>
       <c r="K15" t="n">
-        <v>0.678</v>
+        <v>0.463</v>
       </c>
       <c r="L15" t="n">
-        <v>0.644</v>
+        <v>0.434</v>
       </c>
       <c r="M15" t="n">
-        <v>0.596</v>
+        <v>0.373</v>
       </c>
       <c r="N15" t="n">
-        <v>0.543</v>
+        <v>0.318</v>
       </c>
       <c r="O15" t="n">
-        <v>0.501</v>
+        <v>0.286</v>
       </c>
       <c r="P15" t="n">
-        <v>0.451</v>
+        <v>0.231</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.368</v>
+        <v>0.186</v>
       </c>
       <c r="R15" t="n">
-        <v>0.286</v>
+        <v>0.129</v>
       </c>
       <c r="S15" t="n">
-        <v>0.211</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.097</v>
+        <v>0.046</v>
       </c>
       <c r="U15" t="n">
-        <v>0.036</v>
+        <v>0.012</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>occlusion</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>pca1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>random_baseline</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>saliency</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sumDino</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>xrai</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B21" t="n">
         <v>0.86</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C21" t="n">
         <v>0.841</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D21" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E21" t="n">
         <v>0.781</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F21" t="n">
         <v>0.763</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G21" t="n">
         <v>0.73</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H21" t="n">
         <v>0.698</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I21" t="n">
         <v>0.656</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J21" t="n">
         <v>0.603</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K21" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L21" t="n">
         <v>0.504</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M21" t="n">
         <v>0.455</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N21" t="n">
         <v>0.398</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O21" t="n">
         <v>0.35</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P21" t="n">
         <v>0.293</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q21" t="n">
         <v>0.225</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R21" t="n">
         <v>0.155</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S21" t="n">
         <v>0.103</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T21" t="n">
         <v>0.059</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U21" t="n">
         <v>0.019</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results/excel_reports/vgg16_resnet50_random_noise.xlsx
+++ b/results/excel_reports/vgg16_resnet50_random_noise.xlsx
@@ -784,38 +784,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="19"/>
-          <order val="19"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$21:$V$21</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -889,7 +857,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1199,7 +1167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2349,138 +2317,138 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pca1</t>
+          <t>random_baseline</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0.86</v>
       </c>
       <c r="C17" t="n">
-        <v>0.84</v>
+        <v>0.618</v>
       </c>
       <c r="D17" t="n">
-        <v>0.827</v>
+        <v>0.545</v>
       </c>
       <c r="E17" t="n">
-        <v>0.805</v>
+        <v>0.459</v>
       </c>
       <c r="F17" t="n">
-        <v>0.777</v>
+        <v>0.398</v>
       </c>
       <c r="G17" t="n">
-        <v>0.778</v>
+        <v>0.328</v>
       </c>
       <c r="H17" t="n">
-        <v>0.74</v>
+        <v>0.273</v>
       </c>
       <c r="I17" t="n">
-        <v>0.717</v>
+        <v>0.22</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.169</v>
       </c>
       <c r="K17" t="n">
-        <v>0.64</v>
+        <v>0.134</v>
       </c>
       <c r="L17" t="n">
-        <v>0.595</v>
+        <v>0.101</v>
       </c>
       <c r="M17" t="n">
-        <v>0.555</v>
+        <v>0.076</v>
       </c>
       <c r="N17" t="n">
-        <v>0.526</v>
+        <v>0.055</v>
       </c>
       <c r="O17" t="n">
-        <v>0.461</v>
+        <v>0.035</v>
       </c>
       <c r="P17" t="n">
-        <v>0.392</v>
+        <v>0.027</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.306</v>
+        <v>0.017</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>0.008</v>
       </c>
       <c r="S17" t="n">
-        <v>0.148</v>
+        <v>0.003</v>
       </c>
       <c r="T17" t="n">
-        <v>0.065</v>
+        <v>0.003</v>
       </c>
       <c r="U17" t="n">
-        <v>0.019</v>
+        <v>0.002</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0.86</v>
       </c>
       <c r="C18" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.618</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.459</v>
-      </c>
       <c r="F18" t="n">
-        <v>0.398</v>
+        <v>0.574</v>
       </c>
       <c r="G18" t="n">
-        <v>0.328</v>
+        <v>0.521</v>
       </c>
       <c r="H18" t="n">
-        <v>0.273</v>
+        <v>0.488</v>
       </c>
       <c r="I18" t="n">
-        <v>0.22</v>
+        <v>0.43</v>
       </c>
       <c r="J18" t="n">
-        <v>0.169</v>
+        <v>0.386</v>
       </c>
       <c r="K18" t="n">
-        <v>0.134</v>
+        <v>0.355</v>
       </c>
       <c r="L18" t="n">
-        <v>0.101</v>
+        <v>0.309</v>
       </c>
       <c r="M18" t="n">
-        <v>0.076</v>
+        <v>0.266</v>
       </c>
       <c r="N18" t="n">
-        <v>0.055</v>
+        <v>0.227</v>
       </c>
       <c r="O18" t="n">
-        <v>0.035</v>
+        <v>0.194</v>
       </c>
       <c r="P18" t="n">
-        <v>0.027</v>
+        <v>0.131</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.017</v>
+        <v>0.095</v>
       </c>
       <c r="R18" t="n">
-        <v>0.008</v>
+        <v>0.064</v>
       </c>
       <c r="S18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="U18" t="n">
         <v>0.003</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.002</v>
       </c>
       <c r="V18" t="n">
         <v>0.001</v>
@@ -2489,210 +2457,140 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>sumDino</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0.86</v>
       </c>
       <c r="C19" t="n">
-        <v>0.743</v>
+        <v>0.831</v>
       </c>
       <c r="D19" t="n">
-        <v>0.671</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.618</v>
+        <v>0.8</v>
       </c>
       <c r="F19" t="n">
-        <v>0.574</v>
+        <v>0.773</v>
       </c>
       <c r="G19" t="n">
-        <v>0.521</v>
+        <v>0.758</v>
       </c>
       <c r="H19" t="n">
-        <v>0.488</v>
+        <v>0.721</v>
       </c>
       <c r="I19" t="n">
-        <v>0.43</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.386</v>
+        <v>0.653</v>
       </c>
       <c r="K19" t="n">
-        <v>0.355</v>
+        <v>0.591</v>
       </c>
       <c r="L19" t="n">
-        <v>0.309</v>
+        <v>0.535</v>
       </c>
       <c r="M19" t="n">
-        <v>0.266</v>
+        <v>0.494</v>
       </c>
       <c r="N19" t="n">
-        <v>0.227</v>
+        <v>0.46</v>
       </c>
       <c r="O19" t="n">
-        <v>0.194</v>
+        <v>0.396</v>
       </c>
       <c r="P19" t="n">
-        <v>0.131</v>
+        <v>0.346</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.095</v>
+        <v>0.291</v>
       </c>
       <c r="R19" t="n">
-        <v>0.064</v>
+        <v>0.233</v>
       </c>
       <c r="S19" t="n">
-        <v>0.03</v>
+        <v>0.179</v>
       </c>
       <c r="T19" t="n">
-        <v>0.016</v>
+        <v>0.101</v>
       </c>
       <c r="U19" t="n">
-        <v>0.003</v>
+        <v>0.04</v>
       </c>
       <c r="V19" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sumDino</t>
+          <t>xrai</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0.86</v>
       </c>
       <c r="C20" t="n">
-        <v>0.831</v>
+        <v>0.841</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8</v>
+        <v>0.781</v>
       </c>
       <c r="F20" t="n">
-        <v>0.773</v>
+        <v>0.763</v>
       </c>
       <c r="G20" t="n">
-        <v>0.758</v>
+        <v>0.73</v>
       </c>
       <c r="H20" t="n">
-        <v>0.721</v>
+        <v>0.698</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.656</v>
       </c>
       <c r="J20" t="n">
-        <v>0.653</v>
+        <v>0.603</v>
       </c>
       <c r="K20" t="n">
-        <v>0.591</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.535</v>
+        <v>0.504</v>
       </c>
       <c r="M20" t="n">
-        <v>0.494</v>
+        <v>0.455</v>
       </c>
       <c r="N20" t="n">
-        <v>0.46</v>
+        <v>0.398</v>
       </c>
       <c r="O20" t="n">
-        <v>0.396</v>
+        <v>0.35</v>
       </c>
       <c r="P20" t="n">
-        <v>0.346</v>
+        <v>0.293</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.291</v>
+        <v>0.225</v>
       </c>
       <c r="R20" t="n">
-        <v>0.233</v>
+        <v>0.155</v>
       </c>
       <c r="S20" t="n">
-        <v>0.179</v>
+        <v>0.103</v>
       </c>
       <c r="T20" t="n">
-        <v>0.101</v>
+        <v>0.059</v>
       </c>
       <c r="U20" t="n">
-        <v>0.04</v>
+        <v>0.019</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>xrai</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.841</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="V21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results/excel_reports/vgg16_resnet50_random_noise.xlsx
+++ b/results/excel_reports/vgg16_resnet50_random_noise.xlsx
@@ -784,6 +784,38 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="19"/>
+          <order val="19"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$21:$V$21</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -857,7 +889,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1167,10 +1199,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
@@ -1337,68 +1369,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_FIXED</t>
+          <t>dinov2_COMBO_ENT_SMOOTH</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.86</v>
       </c>
       <c r="C3" t="n">
-        <v>0.836</v>
+        <v>0.844</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.831</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.828</v>
       </c>
       <c r="F3" t="n">
-        <v>0.782</v>
+        <v>0.806</v>
       </c>
       <c r="G3" t="n">
-        <v>0.776</v>
+        <v>0.789</v>
       </c>
       <c r="H3" t="n">
-        <v>0.759</v>
+        <v>0.781</v>
       </c>
       <c r="I3" t="n">
-        <v>0.735</v>
+        <v>0.767</v>
       </c>
       <c r="J3" t="n">
-        <v>0.699</v>
+        <v>0.742</v>
       </c>
       <c r="K3" t="n">
-        <v>0.666</v>
+        <v>0.714</v>
       </c>
       <c r="L3" t="n">
-        <v>0.633</v>
+        <v>0.681</v>
       </c>
       <c r="M3" t="n">
-        <v>0.585</v>
+        <v>0.635</v>
       </c>
       <c r="N3" t="n">
-        <v>0.533</v>
+        <v>0.605</v>
       </c>
       <c r="O3" t="n">
-        <v>0.488</v>
+        <v>0.544</v>
       </c>
       <c r="P3" t="n">
-        <v>0.414</v>
+        <v>0.499</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.338</v>
+        <v>0.412</v>
       </c>
       <c r="R3" t="n">
-        <v>0.274</v>
+        <v>0.339</v>
       </c>
       <c r="S3" t="n">
-        <v>0.187</v>
+        <v>0.259</v>
       </c>
       <c r="T3" t="n">
-        <v>0.098</v>
+        <v>0.178</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03</v>
+        <v>0.073</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -1407,163 +1439,163 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dinov2_ENT</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.86</v>
       </c>
       <c r="C4" t="n">
-        <v>0.827</v>
+        <v>0.836</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.787</v>
+        <v>0.782</v>
       </c>
       <c r="G4" t="n">
-        <v>0.769</v>
+        <v>0.776</v>
       </c>
       <c r="H4" t="n">
-        <v>0.75</v>
+        <v>0.759</v>
       </c>
       <c r="I4" t="n">
-        <v>0.719</v>
+        <v>0.735</v>
       </c>
       <c r="J4" t="n">
-        <v>0.704</v>
+        <v>0.699</v>
       </c>
       <c r="K4" t="n">
         <v>0.666</v>
       </c>
       <c r="L4" t="n">
-        <v>0.619</v>
+        <v>0.633</v>
       </c>
       <c r="M4" t="n">
-        <v>0.578</v>
+        <v>0.585</v>
       </c>
       <c r="N4" t="n">
-        <v>0.528</v>
+        <v>0.533</v>
       </c>
       <c r="O4" t="n">
-        <v>0.491</v>
+        <v>0.488</v>
       </c>
       <c r="P4" t="n">
-        <v>0.415</v>
+        <v>0.414</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.355</v>
+        <v>0.338</v>
       </c>
       <c r="R4" t="n">
-        <v>0.281</v>
+        <v>0.274</v>
       </c>
       <c r="S4" t="n">
-        <v>0.207</v>
+        <v>0.187</v>
       </c>
       <c r="T4" t="n">
-        <v>0.123</v>
+        <v>0.098</v>
       </c>
       <c r="U4" t="n">
-        <v>0.051</v>
+        <v>0.03</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dinov2_PC1</t>
+          <t>dinov2_ENT</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.86</v>
       </c>
       <c r="C5" t="n">
-        <v>0.833</v>
+        <v>0.827</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.802</v>
+        <v>0.806</v>
       </c>
       <c r="F5" t="n">
-        <v>0.789</v>
+        <v>0.787</v>
       </c>
       <c r="G5" t="n">
-        <v>0.781</v>
+        <v>0.769</v>
       </c>
       <c r="H5" t="n">
-        <v>0.768</v>
+        <v>0.75</v>
       </c>
       <c r="I5" t="n">
-        <v>0.727</v>
+        <v>0.719</v>
       </c>
       <c r="J5" t="n">
-        <v>0.703</v>
+        <v>0.704</v>
       </c>
       <c r="K5" t="n">
-        <v>0.656</v>
+        <v>0.666</v>
       </c>
       <c r="L5" t="n">
-        <v>0.615</v>
+        <v>0.619</v>
       </c>
       <c r="M5" t="n">
-        <v>0.576</v>
+        <v>0.578</v>
       </c>
       <c r="N5" t="n">
-        <v>0.521</v>
+        <v>0.528</v>
       </c>
       <c r="O5" t="n">
-        <v>0.465</v>
+        <v>0.491</v>
       </c>
       <c r="P5" t="n">
-        <v>0.399</v>
+        <v>0.415</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.326</v>
+        <v>0.355</v>
       </c>
       <c r="R5" t="n">
-        <v>0.243</v>
+        <v>0.281</v>
       </c>
       <c r="S5" t="n">
-        <v>0.142</v>
+        <v>0.207</v>
       </c>
       <c r="T5" t="n">
-        <v>0.063</v>
+        <v>0.123</v>
       </c>
       <c r="U5" t="n">
-        <v>0.018</v>
+        <v>0.051</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dinov2_PC_EV</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.86</v>
       </c>
       <c r="C6" t="n">
-        <v>0.832</v>
+        <v>0.833</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.804</v>
+        <v>0.802</v>
       </c>
       <c r="F6" t="n">
-        <v>0.79</v>
+        <v>0.789</v>
       </c>
       <c r="G6" t="n">
         <v>0.781</v>
@@ -1572,43 +1604,43 @@
         <v>0.768</v>
       </c>
       <c r="I6" t="n">
-        <v>0.73</v>
+        <v>0.727</v>
       </c>
       <c r="J6" t="n">
-        <v>0.698</v>
+        <v>0.703</v>
       </c>
       <c r="K6" t="n">
-        <v>0.658</v>
+        <v>0.656</v>
       </c>
       <c r="L6" t="n">
-        <v>0.618</v>
+        <v>0.615</v>
       </c>
       <c r="M6" t="n">
-        <v>0.569</v>
+        <v>0.576</v>
       </c>
       <c r="N6" t="n">
-        <v>0.528</v>
+        <v>0.521</v>
       </c>
       <c r="O6" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="P6" t="n">
-        <v>0.389</v>
+        <v>0.399</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.324</v>
+        <v>0.326</v>
       </c>
       <c r="R6" t="n">
-        <v>0.24</v>
+        <v>0.243</v>
       </c>
       <c r="S6" t="n">
-        <v>0.136</v>
+        <v>0.142</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="U6" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="V6" t="n">
         <v>0.001</v>
@@ -1617,208 +1649,208 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dinov2_PC_L2</t>
+          <t>dinov2_PC_EV</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.86</v>
       </c>
       <c r="C7" t="n">
-        <v>0.791</v>
+        <v>0.832</v>
       </c>
       <c r="D7" t="n">
-        <v>0.755</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.723</v>
+        <v>0.804</v>
       </c>
       <c r="F7" t="n">
-        <v>0.677</v>
+        <v>0.79</v>
       </c>
       <c r="G7" t="n">
-        <v>0.62</v>
+        <v>0.781</v>
       </c>
       <c r="H7" t="n">
-        <v>0.572</v>
+        <v>0.768</v>
       </c>
       <c r="I7" t="n">
-        <v>0.523</v>
+        <v>0.73</v>
       </c>
       <c r="J7" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="O7" t="n">
         <v>0.464</v>
       </c>
-      <c r="K7" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.247</v>
-      </c>
       <c r="P7" t="n">
-        <v>0.215</v>
+        <v>0.389</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.195</v>
+        <v>0.324</v>
       </c>
       <c r="R7" t="n">
-        <v>0.152</v>
+        <v>0.24</v>
       </c>
       <c r="S7" t="n">
-        <v>0.106</v>
+        <v>0.136</v>
       </c>
       <c r="T7" t="n">
-        <v>0.053</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>dinov2_PC_L2</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.86</v>
       </c>
       <c r="C8" t="n">
-        <v>0.821</v>
+        <v>0.791</v>
       </c>
       <c r="D8" t="n">
-        <v>0.798</v>
+        <v>0.755</v>
       </c>
       <c r="E8" t="n">
-        <v>0.775</v>
+        <v>0.723</v>
       </c>
       <c r="F8" t="n">
-        <v>0.756</v>
+        <v>0.677</v>
       </c>
       <c r="G8" t="n">
-        <v>0.732</v>
+        <v>0.62</v>
       </c>
       <c r="H8" t="n">
-        <v>0.705</v>
+        <v>0.572</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.523</v>
       </c>
       <c r="J8" t="n">
-        <v>0.635</v>
+        <v>0.464</v>
       </c>
       <c r="K8" t="n">
-        <v>0.614</v>
+        <v>0.41</v>
       </c>
       <c r="L8" t="n">
-        <v>0.571</v>
+        <v>0.357</v>
       </c>
       <c r="M8" t="n">
-        <v>0.524</v>
+        <v>0.317</v>
       </c>
       <c r="N8" t="n">
-        <v>0.486</v>
+        <v>0.278</v>
       </c>
       <c r="O8" t="n">
-        <v>0.435</v>
+        <v>0.247</v>
       </c>
       <c r="P8" t="n">
-        <v>0.374</v>
+        <v>0.215</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.322</v>
+        <v>0.195</v>
       </c>
       <c r="R8" t="n">
-        <v>0.258</v>
+        <v>0.152</v>
       </c>
       <c r="S8" t="n">
-        <v>0.186</v>
+        <v>0.106</v>
       </c>
       <c r="T8" t="n">
-        <v>0.12</v>
+        <v>0.053</v>
       </c>
       <c r="U8" t="n">
-        <v>0.049</v>
+        <v>0.021</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dinov2_pca_gaussian</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.86</v>
       </c>
       <c r="C9" t="n">
-        <v>0.855</v>
+        <v>0.821</v>
       </c>
       <c r="D9" t="n">
-        <v>0.828</v>
+        <v>0.798</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="F9" t="n">
-        <v>0.794</v>
+        <v>0.756</v>
       </c>
       <c r="G9" t="n">
-        <v>0.772</v>
+        <v>0.732</v>
       </c>
       <c r="H9" t="n">
-        <v>0.745</v>
+        <v>0.705</v>
       </c>
       <c r="I9" t="n">
-        <v>0.717</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.635</v>
       </c>
       <c r="K9" t="n">
-        <v>0.645</v>
+        <v>0.614</v>
       </c>
       <c r="L9" t="n">
-        <v>0.612</v>
+        <v>0.571</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.524</v>
       </c>
       <c r="N9" t="n">
-        <v>0.533</v>
+        <v>0.486</v>
       </c>
       <c r="O9" t="n">
-        <v>0.471</v>
+        <v>0.435</v>
       </c>
       <c r="P9" t="n">
-        <v>0.399</v>
+        <v>0.374</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.333</v>
+        <v>0.322</v>
       </c>
       <c r="R9" t="n">
-        <v>0.248</v>
+        <v>0.258</v>
       </c>
       <c r="S9" t="n">
-        <v>0.177</v>
+        <v>0.186</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="U9" t="n">
-        <v>0.032</v>
+        <v>0.049</v>
       </c>
       <c r="V9" t="n">
         <v>0.001</v>
@@ -1827,138 +1859,138 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>dinov2_pca_gaussian</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.86</v>
       </c>
       <c r="C10" t="n">
-        <v>0.795</v>
+        <v>0.855</v>
       </c>
       <c r="D10" t="n">
-        <v>0.751</v>
+        <v>0.828</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.641</v>
+        <v>0.794</v>
       </c>
       <c r="G10" t="n">
-        <v>0.606</v>
+        <v>0.772</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.745</v>
       </c>
       <c r="I10" t="n">
-        <v>0.506</v>
+        <v>0.717</v>
       </c>
       <c r="J10" t="n">
-        <v>0.47</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.423</v>
+        <v>0.645</v>
       </c>
       <c r="L10" t="n">
-        <v>0.391</v>
+        <v>0.612</v>
       </c>
       <c r="M10" t="n">
-        <v>0.329</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.306</v>
+        <v>0.533</v>
       </c>
       <c r="O10" t="n">
-        <v>0.28</v>
+        <v>0.471</v>
       </c>
       <c r="P10" t="n">
-        <v>0.243</v>
+        <v>0.399</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.185</v>
+        <v>0.333</v>
       </c>
       <c r="R10" t="n">
-        <v>0.153</v>
+        <v>0.248</v>
       </c>
       <c r="S10" t="n">
-        <v>0.117</v>
+        <v>0.177</v>
       </c>
       <c r="T10" t="n">
-        <v>0.065</v>
+        <v>0.09</v>
       </c>
       <c r="U10" t="n">
-        <v>0.022</v>
+        <v>0.032</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.86</v>
       </c>
       <c r="C11" t="n">
-        <v>0.786</v>
+        <v>0.795</v>
       </c>
       <c r="D11" t="n">
-        <v>0.739</v>
+        <v>0.751</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.657</v>
+        <v>0.641</v>
       </c>
       <c r="G11" t="n">
-        <v>0.629</v>
+        <v>0.606</v>
       </c>
       <c r="H11" t="n">
-        <v>0.599</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.556</v>
+        <v>0.506</v>
       </c>
       <c r="J11" t="n">
-        <v>0.496</v>
+        <v>0.47</v>
       </c>
       <c r="K11" t="n">
-        <v>0.467</v>
+        <v>0.423</v>
       </c>
       <c r="L11" t="n">
-        <v>0.422</v>
+        <v>0.391</v>
       </c>
       <c r="M11" t="n">
-        <v>0.368</v>
+        <v>0.329</v>
       </c>
       <c r="N11" t="n">
-        <v>0.333</v>
+        <v>0.306</v>
       </c>
       <c r="O11" t="n">
-        <v>0.266</v>
+        <v>0.28</v>
       </c>
       <c r="P11" t="n">
-        <v>0.233</v>
+        <v>0.243</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.186</v>
+        <v>0.185</v>
       </c>
       <c r="R11" t="n">
-        <v>0.122</v>
+        <v>0.153</v>
       </c>
       <c r="S11" t="n">
-        <v>0.079</v>
+        <v>0.117</v>
       </c>
       <c r="T11" t="n">
-        <v>0.037</v>
+        <v>0.065</v>
       </c>
       <c r="U11" t="n">
-        <v>0.007</v>
+        <v>0.022</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1967,138 +1999,138 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.86</v>
       </c>
       <c r="C12" t="n">
-        <v>0.772</v>
+        <v>0.786</v>
       </c>
       <c r="D12" t="n">
-        <v>0.734</v>
+        <v>0.739</v>
       </c>
       <c r="E12" t="n">
-        <v>0.702</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.666</v>
+        <v>0.657</v>
       </c>
       <c r="G12" t="n">
-        <v>0.64</v>
+        <v>0.629</v>
       </c>
       <c r="H12" t="n">
-        <v>0.608</v>
+        <v>0.599</v>
       </c>
       <c r="I12" t="n">
-        <v>0.574</v>
+        <v>0.556</v>
       </c>
       <c r="J12" t="n">
-        <v>0.543</v>
+        <v>0.496</v>
       </c>
       <c r="K12" t="n">
-        <v>0.525</v>
+        <v>0.467</v>
       </c>
       <c r="L12" t="n">
-        <v>0.484</v>
+        <v>0.422</v>
       </c>
       <c r="M12" t="n">
-        <v>0.46</v>
+        <v>0.368</v>
       </c>
       <c r="N12" t="n">
-        <v>0.417</v>
+        <v>0.333</v>
       </c>
       <c r="O12" t="n">
-        <v>0.377</v>
+        <v>0.266</v>
       </c>
       <c r="P12" t="n">
-        <v>0.322</v>
+        <v>0.233</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.288</v>
+        <v>0.186</v>
       </c>
       <c r="R12" t="n">
-        <v>0.229</v>
+        <v>0.122</v>
       </c>
       <c r="S12" t="n">
-        <v>0.165</v>
+        <v>0.079</v>
       </c>
       <c r="T12" t="n">
-        <v>0.103</v>
+        <v>0.037</v>
       </c>
       <c r="U12" t="n">
-        <v>0.034</v>
+        <v>0.007</v>
       </c>
       <c r="V12" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.86</v>
       </c>
       <c r="C13" t="n">
-        <v>0.788</v>
+        <v>0.772</v>
       </c>
       <c r="D13" t="n">
-        <v>0.749</v>
+        <v>0.734</v>
       </c>
       <c r="E13" t="n">
-        <v>0.657</v>
+        <v>0.702</v>
       </c>
       <c r="F13" t="n">
-        <v>0.62</v>
+        <v>0.666</v>
       </c>
       <c r="G13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.574</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.543</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.451</v>
-      </c>
       <c r="K13" t="n">
-        <v>0.397</v>
+        <v>0.525</v>
       </c>
       <c r="L13" t="n">
-        <v>0.347</v>
+        <v>0.484</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="N13" t="n">
-        <v>0.264</v>
+        <v>0.417</v>
       </c>
       <c r="O13" t="n">
-        <v>0.234</v>
+        <v>0.377</v>
       </c>
       <c r="P13" t="n">
-        <v>0.195</v>
+        <v>0.322</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.148</v>
+        <v>0.288</v>
       </c>
       <c r="R13" t="n">
-        <v>0.114</v>
+        <v>0.229</v>
       </c>
       <c r="S13" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.165</v>
       </c>
       <c r="T13" t="n">
-        <v>0.04</v>
+        <v>0.103</v>
       </c>
       <c r="U13" t="n">
-        <v>0.017</v>
+        <v>0.034</v>
       </c>
       <c r="V13" t="n">
         <v>0.002</v>
@@ -2107,68 +2139,68 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.86</v>
       </c>
       <c r="C14" t="n">
-        <v>0.786</v>
+        <v>0.788</v>
       </c>
       <c r="D14" t="n">
-        <v>0.728</v>
+        <v>0.749</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.657</v>
       </c>
       <c r="F14" t="n">
-        <v>0.636</v>
+        <v>0.62</v>
       </c>
       <c r="G14" t="n">
-        <v>0.598</v>
+        <v>0.574</v>
       </c>
       <c r="H14" t="n">
-        <v>0.551</v>
+        <v>0.543</v>
       </c>
       <c r="I14" t="n">
-        <v>0.51</v>
+        <v>0.504</v>
       </c>
       <c r="J14" t="n">
-        <v>0.457</v>
+        <v>0.451</v>
       </c>
       <c r="K14" t="n">
-        <v>0.414</v>
+        <v>0.397</v>
       </c>
       <c r="L14" t="n">
-        <v>0.377</v>
+        <v>0.347</v>
       </c>
       <c r="M14" t="n">
-        <v>0.325</v>
+        <v>0.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.267</v>
+        <v>0.264</v>
       </c>
       <c r="O14" t="n">
-        <v>0.223</v>
+        <v>0.234</v>
       </c>
       <c r="P14" t="n">
-        <v>0.169</v>
+        <v>0.195</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.121</v>
+        <v>0.148</v>
       </c>
       <c r="R14" t="n">
-        <v>0.089</v>
+        <v>0.114</v>
       </c>
       <c r="S14" t="n">
-        <v>0.049</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.023</v>
+        <v>0.04</v>
       </c>
       <c r="U14" t="n">
-        <v>0.007</v>
+        <v>0.017</v>
       </c>
       <c r="V14" t="n">
         <v>0.002</v>
@@ -2177,68 +2209,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0.86</v>
       </c>
       <c r="C15" t="n">
-        <v>0.783</v>
+        <v>0.786</v>
       </c>
       <c r="D15" t="n">
-        <v>0.734</v>
+        <v>0.728</v>
       </c>
       <c r="E15" t="n">
-        <v>0.705</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.657</v>
+        <v>0.636</v>
       </c>
       <c r="G15" t="n">
-        <v>0.635</v>
+        <v>0.598</v>
       </c>
       <c r="H15" t="n">
-        <v>0.591</v>
+        <v>0.551</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="J15" t="n">
-        <v>0.516</v>
+        <v>0.457</v>
       </c>
       <c r="K15" t="n">
-        <v>0.463</v>
+        <v>0.414</v>
       </c>
       <c r="L15" t="n">
-        <v>0.434</v>
+        <v>0.377</v>
       </c>
       <c r="M15" t="n">
-        <v>0.373</v>
+        <v>0.325</v>
       </c>
       <c r="N15" t="n">
-        <v>0.318</v>
+        <v>0.267</v>
       </c>
       <c r="O15" t="n">
-        <v>0.286</v>
+        <v>0.223</v>
       </c>
       <c r="P15" t="n">
-        <v>0.231</v>
+        <v>0.169</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.186</v>
+        <v>0.121</v>
       </c>
       <c r="R15" t="n">
-        <v>0.129</v>
+        <v>0.089</v>
       </c>
       <c r="S15" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.049</v>
       </c>
       <c r="T15" t="n">
-        <v>0.046</v>
+        <v>0.023</v>
       </c>
       <c r="U15" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="V15" t="n">
         <v>0.002</v>
@@ -2247,138 +2279,138 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0.86</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.783</v>
       </c>
       <c r="D16" t="n">
-        <v>0.771</v>
+        <v>0.734</v>
       </c>
       <c r="E16" t="n">
-        <v>0.724</v>
+        <v>0.705</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.657</v>
       </c>
       <c r="G16" t="n">
-        <v>0.641</v>
+        <v>0.635</v>
       </c>
       <c r="H16" t="n">
-        <v>0.612</v>
+        <v>0.591</v>
       </c>
       <c r="I16" t="n">
-        <v>0.547</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.509</v>
+        <v>0.516</v>
       </c>
       <c r="K16" t="n">
-        <v>0.455</v>
+        <v>0.463</v>
       </c>
       <c r="L16" t="n">
-        <v>0.417</v>
+        <v>0.434</v>
       </c>
       <c r="M16" t="n">
-        <v>0.366</v>
+        <v>0.373</v>
       </c>
       <c r="N16" t="n">
-        <v>0.331</v>
+        <v>0.318</v>
       </c>
       <c r="O16" t="n">
-        <v>0.298</v>
+        <v>0.286</v>
       </c>
       <c r="P16" t="n">
-        <v>0.263</v>
+        <v>0.231</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.217</v>
+        <v>0.186</v>
       </c>
       <c r="R16" t="n">
-        <v>0.161</v>
+        <v>0.129</v>
       </c>
       <c r="S16" t="n">
-        <v>0.139</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.046</v>
       </c>
       <c r="U16" t="n">
-        <v>0.026</v>
+        <v>0.012</v>
       </c>
       <c r="V16" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0.86</v>
       </c>
       <c r="C17" t="n">
-        <v>0.618</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.545</v>
+        <v>0.771</v>
       </c>
       <c r="E17" t="n">
-        <v>0.459</v>
+        <v>0.724</v>
       </c>
       <c r="F17" t="n">
-        <v>0.398</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.328</v>
+        <v>0.641</v>
       </c>
       <c r="H17" t="n">
-        <v>0.273</v>
+        <v>0.612</v>
       </c>
       <c r="I17" t="n">
-        <v>0.22</v>
+        <v>0.547</v>
       </c>
       <c r="J17" t="n">
-        <v>0.169</v>
+        <v>0.509</v>
       </c>
       <c r="K17" t="n">
-        <v>0.134</v>
+        <v>0.455</v>
       </c>
       <c r="L17" t="n">
-        <v>0.101</v>
+        <v>0.417</v>
       </c>
       <c r="M17" t="n">
-        <v>0.076</v>
+        <v>0.366</v>
       </c>
       <c r="N17" t="n">
-        <v>0.055</v>
+        <v>0.331</v>
       </c>
       <c r="O17" t="n">
-        <v>0.035</v>
+        <v>0.298</v>
       </c>
       <c r="P17" t="n">
-        <v>0.027</v>
+        <v>0.263</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.017</v>
+        <v>0.217</v>
       </c>
       <c r="R17" t="n">
-        <v>0.008</v>
+        <v>0.161</v>
       </c>
       <c r="S17" t="n">
-        <v>0.003</v>
+        <v>0.139</v>
       </c>
       <c r="T17" t="n">
-        <v>0.003</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.002</v>
+        <v>0.026</v>
       </c>
       <c r="V17" t="n">
         <v>0.001</v>
@@ -2387,68 +2419,68 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>random_baseline</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0.86</v>
       </c>
       <c r="C18" t="n">
-        <v>0.743</v>
+        <v>0.618</v>
       </c>
       <c r="D18" t="n">
-        <v>0.671</v>
+        <v>0.545</v>
       </c>
       <c r="E18" t="n">
-        <v>0.618</v>
+        <v>0.459</v>
       </c>
       <c r="F18" t="n">
-        <v>0.574</v>
+        <v>0.398</v>
       </c>
       <c r="G18" t="n">
-        <v>0.521</v>
+        <v>0.328</v>
       </c>
       <c r="H18" t="n">
-        <v>0.488</v>
+        <v>0.273</v>
       </c>
       <c r="I18" t="n">
-        <v>0.43</v>
+        <v>0.22</v>
       </c>
       <c r="J18" t="n">
-        <v>0.386</v>
+        <v>0.169</v>
       </c>
       <c r="K18" t="n">
-        <v>0.355</v>
+        <v>0.134</v>
       </c>
       <c r="L18" t="n">
-        <v>0.309</v>
+        <v>0.101</v>
       </c>
       <c r="M18" t="n">
-        <v>0.266</v>
+        <v>0.076</v>
       </c>
       <c r="N18" t="n">
-        <v>0.227</v>
+        <v>0.055</v>
       </c>
       <c r="O18" t="n">
-        <v>0.194</v>
+        <v>0.035</v>
       </c>
       <c r="P18" t="n">
-        <v>0.131</v>
+        <v>0.027</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.095</v>
+        <v>0.017</v>
       </c>
       <c r="R18" t="n">
-        <v>0.064</v>
+        <v>0.008</v>
       </c>
       <c r="S18" t="n">
-        <v>0.03</v>
+        <v>0.003</v>
       </c>
       <c r="T18" t="n">
-        <v>0.016</v>
+        <v>0.003</v>
       </c>
       <c r="U18" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="V18" t="n">
         <v>0.001</v>
@@ -2457,140 +2489,210 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sumDino</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0.86</v>
       </c>
       <c r="C19" t="n">
-        <v>0.831</v>
+        <v>0.743</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.671</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8</v>
+        <v>0.618</v>
       </c>
       <c r="F19" t="n">
-        <v>0.773</v>
+        <v>0.574</v>
       </c>
       <c r="G19" t="n">
-        <v>0.758</v>
+        <v>0.521</v>
       </c>
       <c r="H19" t="n">
-        <v>0.721</v>
+        <v>0.488</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="J19" t="n">
-        <v>0.653</v>
+        <v>0.386</v>
       </c>
       <c r="K19" t="n">
-        <v>0.591</v>
+        <v>0.355</v>
       </c>
       <c r="L19" t="n">
-        <v>0.535</v>
+        <v>0.309</v>
       </c>
       <c r="M19" t="n">
-        <v>0.494</v>
+        <v>0.266</v>
       </c>
       <c r="N19" t="n">
-        <v>0.46</v>
+        <v>0.227</v>
       </c>
       <c r="O19" t="n">
-        <v>0.396</v>
+        <v>0.194</v>
       </c>
       <c r="P19" t="n">
-        <v>0.346</v>
+        <v>0.131</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.291</v>
+        <v>0.095</v>
       </c>
       <c r="R19" t="n">
-        <v>0.233</v>
+        <v>0.064</v>
       </c>
       <c r="S19" t="n">
-        <v>0.179</v>
+        <v>0.03</v>
       </c>
       <c r="T19" t="n">
-        <v>0.101</v>
+        <v>0.016</v>
       </c>
       <c r="U19" t="n">
-        <v>0.04</v>
+        <v>0.003</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>sumDino</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>xrai</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>0.86</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>0.841</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>0.781</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>0.763</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>0.73</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>0.698</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>0.656</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>0.603</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>0.504</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>0.455</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>0.398</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>0.35</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>0.293</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>0.225</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>0.155</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>0.103</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>0.059</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>0.019</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results/excel_reports/vgg16_resnet50_random_noise.xlsx
+++ b/results/excel_reports/vgg16_resnet50_random_noise.xlsx
@@ -784,38 +784,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="19"/>
-          <order val="19"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$21:$V$21</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -889,7 +857,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1199,7 +1167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1376,64 +1344,64 @@
         <v>0.86</v>
       </c>
       <c r="C3" t="n">
-        <v>0.844</v>
+        <v>0.842</v>
       </c>
       <c r="D3" t="n">
-        <v>0.831</v>
+        <v>0.839</v>
       </c>
       <c r="E3" t="n">
-        <v>0.828</v>
+        <v>0.826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.806</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.789</v>
+        <v>0.804</v>
       </c>
       <c r="H3" t="n">
-        <v>0.781</v>
+        <v>0.791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.767</v>
+        <v>0.777</v>
       </c>
       <c r="J3" t="n">
-        <v>0.742</v>
+        <v>0.752</v>
       </c>
       <c r="K3" t="n">
-        <v>0.714</v>
+        <v>0.725</v>
       </c>
       <c r="L3" t="n">
-        <v>0.681</v>
+        <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0.635</v>
+        <v>0.664</v>
       </c>
       <c r="N3" t="n">
-        <v>0.605</v>
+        <v>0.615</v>
       </c>
       <c r="O3" t="n">
-        <v>0.544</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.499</v>
+        <v>0.512</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.412</v>
+        <v>0.436</v>
       </c>
       <c r="R3" t="n">
-        <v>0.339</v>
+        <v>0.364</v>
       </c>
       <c r="S3" t="n">
-        <v>0.259</v>
+        <v>0.271</v>
       </c>
       <c r="T3" t="n">
-        <v>0.178</v>
+        <v>0.199</v>
       </c>
       <c r="U3" t="n">
-        <v>0.073</v>
+        <v>0.083</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="4">
@@ -1859,138 +1827,138 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dinov2_pca_gaussian</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.86</v>
       </c>
       <c r="C10" t="n">
-        <v>0.855</v>
+        <v>0.795</v>
       </c>
       <c r="D10" t="n">
-        <v>0.828</v>
+        <v>0.751</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.794</v>
+        <v>0.641</v>
       </c>
       <c r="G10" t="n">
-        <v>0.772</v>
+        <v>0.606</v>
       </c>
       <c r="H10" t="n">
-        <v>0.745</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.717</v>
+        <v>0.506</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="K10" t="n">
-        <v>0.645</v>
+        <v>0.423</v>
       </c>
       <c r="L10" t="n">
-        <v>0.612</v>
+        <v>0.391</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.329</v>
       </c>
       <c r="N10" t="n">
-        <v>0.533</v>
+        <v>0.306</v>
       </c>
       <c r="O10" t="n">
-        <v>0.471</v>
+        <v>0.28</v>
       </c>
       <c r="P10" t="n">
-        <v>0.399</v>
+        <v>0.243</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.333</v>
+        <v>0.185</v>
       </c>
       <c r="R10" t="n">
-        <v>0.248</v>
+        <v>0.153</v>
       </c>
       <c r="S10" t="n">
-        <v>0.177</v>
+        <v>0.117</v>
       </c>
       <c r="T10" t="n">
-        <v>0.09</v>
+        <v>0.065</v>
       </c>
       <c r="U10" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.86</v>
       </c>
       <c r="C11" t="n">
-        <v>0.795</v>
+        <v>0.786</v>
       </c>
       <c r="D11" t="n">
-        <v>0.751</v>
+        <v>0.739</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.641</v>
+        <v>0.657</v>
       </c>
       <c r="G11" t="n">
-        <v>0.606</v>
+        <v>0.629</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.599</v>
       </c>
       <c r="I11" t="n">
-        <v>0.506</v>
+        <v>0.556</v>
       </c>
       <c r="J11" t="n">
-        <v>0.47</v>
+        <v>0.496</v>
       </c>
       <c r="K11" t="n">
-        <v>0.423</v>
+        <v>0.467</v>
       </c>
       <c r="L11" t="n">
-        <v>0.391</v>
+        <v>0.422</v>
       </c>
       <c r="M11" t="n">
-        <v>0.329</v>
+        <v>0.368</v>
       </c>
       <c r="N11" t="n">
-        <v>0.306</v>
+        <v>0.333</v>
       </c>
       <c r="O11" t="n">
-        <v>0.28</v>
+        <v>0.266</v>
       </c>
       <c r="P11" t="n">
-        <v>0.243</v>
+        <v>0.233</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.185</v>
+        <v>0.186</v>
       </c>
       <c r="R11" t="n">
-        <v>0.153</v>
+        <v>0.122</v>
       </c>
       <c r="S11" t="n">
-        <v>0.117</v>
+        <v>0.079</v>
       </c>
       <c r="T11" t="n">
-        <v>0.065</v>
+        <v>0.037</v>
       </c>
       <c r="U11" t="n">
-        <v>0.022</v>
+        <v>0.007</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1999,138 +1967,138 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.86</v>
       </c>
       <c r="C12" t="n">
-        <v>0.786</v>
+        <v>0.772</v>
       </c>
       <c r="D12" t="n">
-        <v>0.739</v>
+        <v>0.734</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.702</v>
       </c>
       <c r="F12" t="n">
-        <v>0.657</v>
+        <v>0.666</v>
       </c>
       <c r="G12" t="n">
-        <v>0.629</v>
+        <v>0.64</v>
       </c>
       <c r="H12" t="n">
-        <v>0.599</v>
+        <v>0.608</v>
       </c>
       <c r="I12" t="n">
-        <v>0.556</v>
+        <v>0.574</v>
       </c>
       <c r="J12" t="n">
-        <v>0.496</v>
+        <v>0.543</v>
       </c>
       <c r="K12" t="n">
-        <v>0.467</v>
+        <v>0.525</v>
       </c>
       <c r="L12" t="n">
-        <v>0.422</v>
+        <v>0.484</v>
       </c>
       <c r="M12" t="n">
-        <v>0.368</v>
+        <v>0.46</v>
       </c>
       <c r="N12" t="n">
-        <v>0.333</v>
+        <v>0.417</v>
       </c>
       <c r="O12" t="n">
-        <v>0.266</v>
+        <v>0.377</v>
       </c>
       <c r="P12" t="n">
-        <v>0.233</v>
+        <v>0.322</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.186</v>
+        <v>0.288</v>
       </c>
       <c r="R12" t="n">
-        <v>0.122</v>
+        <v>0.229</v>
       </c>
       <c r="S12" t="n">
-        <v>0.079</v>
+        <v>0.165</v>
       </c>
       <c r="T12" t="n">
-        <v>0.037</v>
+        <v>0.103</v>
       </c>
       <c r="U12" t="n">
-        <v>0.007</v>
+        <v>0.034</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.86</v>
       </c>
       <c r="C13" t="n">
-        <v>0.772</v>
+        <v>0.788</v>
       </c>
       <c r="D13" t="n">
-        <v>0.734</v>
+        <v>0.749</v>
       </c>
       <c r="E13" t="n">
-        <v>0.702</v>
+        <v>0.657</v>
       </c>
       <c r="F13" t="n">
-        <v>0.666</v>
+        <v>0.62</v>
       </c>
       <c r="G13" t="n">
-        <v>0.64</v>
+        <v>0.574</v>
       </c>
       <c r="H13" t="n">
-        <v>0.608</v>
+        <v>0.543</v>
       </c>
       <c r="I13" t="n">
-        <v>0.574</v>
+        <v>0.504</v>
       </c>
       <c r="J13" t="n">
-        <v>0.543</v>
+        <v>0.451</v>
       </c>
       <c r="K13" t="n">
-        <v>0.525</v>
+        <v>0.397</v>
       </c>
       <c r="L13" t="n">
-        <v>0.484</v>
+        <v>0.347</v>
       </c>
       <c r="M13" t="n">
-        <v>0.46</v>
+        <v>0.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.417</v>
+        <v>0.264</v>
       </c>
       <c r="O13" t="n">
-        <v>0.377</v>
+        <v>0.234</v>
       </c>
       <c r="P13" t="n">
-        <v>0.322</v>
+        <v>0.195</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.288</v>
+        <v>0.148</v>
       </c>
       <c r="R13" t="n">
-        <v>0.229</v>
+        <v>0.114</v>
       </c>
       <c r="S13" t="n">
-        <v>0.165</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.103</v>
+        <v>0.04</v>
       </c>
       <c r="U13" t="n">
-        <v>0.034</v>
+        <v>0.017</v>
       </c>
       <c r="V13" t="n">
         <v>0.002</v>
@@ -2139,68 +2107,68 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.86</v>
       </c>
       <c r="C14" t="n">
-        <v>0.788</v>
+        <v>0.786</v>
       </c>
       <c r="D14" t="n">
-        <v>0.749</v>
+        <v>0.728</v>
       </c>
       <c r="E14" t="n">
-        <v>0.657</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.62</v>
+        <v>0.636</v>
       </c>
       <c r="G14" t="n">
-        <v>0.574</v>
+        <v>0.598</v>
       </c>
       <c r="H14" t="n">
-        <v>0.543</v>
+        <v>0.551</v>
       </c>
       <c r="I14" t="n">
-        <v>0.504</v>
+        <v>0.51</v>
       </c>
       <c r="J14" t="n">
-        <v>0.451</v>
+        <v>0.457</v>
       </c>
       <c r="K14" t="n">
-        <v>0.397</v>
+        <v>0.414</v>
       </c>
       <c r="L14" t="n">
-        <v>0.347</v>
+        <v>0.377</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3</v>
+        <v>0.325</v>
       </c>
       <c r="N14" t="n">
-        <v>0.264</v>
+        <v>0.267</v>
       </c>
       <c r="O14" t="n">
-        <v>0.234</v>
+        <v>0.223</v>
       </c>
       <c r="P14" t="n">
-        <v>0.195</v>
+        <v>0.169</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.148</v>
+        <v>0.121</v>
       </c>
       <c r="R14" t="n">
-        <v>0.114</v>
+        <v>0.089</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.049</v>
       </c>
       <c r="T14" t="n">
-        <v>0.04</v>
+        <v>0.023</v>
       </c>
       <c r="U14" t="n">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
       <c r="V14" t="n">
         <v>0.002</v>
@@ -2209,68 +2177,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0.86</v>
       </c>
       <c r="C15" t="n">
-        <v>0.786</v>
+        <v>0.783</v>
       </c>
       <c r="D15" t="n">
-        <v>0.728</v>
+        <v>0.734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.705</v>
       </c>
       <c r="F15" t="n">
-        <v>0.636</v>
+        <v>0.657</v>
       </c>
       <c r="G15" t="n">
-        <v>0.598</v>
+        <v>0.635</v>
       </c>
       <c r="H15" t="n">
-        <v>0.551</v>
+        <v>0.591</v>
       </c>
       <c r="I15" t="n">
-        <v>0.51</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.457</v>
+        <v>0.516</v>
       </c>
       <c r="K15" t="n">
-        <v>0.414</v>
+        <v>0.463</v>
       </c>
       <c r="L15" t="n">
-        <v>0.377</v>
+        <v>0.434</v>
       </c>
       <c r="M15" t="n">
-        <v>0.325</v>
+        <v>0.373</v>
       </c>
       <c r="N15" t="n">
-        <v>0.267</v>
+        <v>0.318</v>
       </c>
       <c r="O15" t="n">
-        <v>0.223</v>
+        <v>0.286</v>
       </c>
       <c r="P15" t="n">
-        <v>0.169</v>
+        <v>0.231</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.121</v>
+        <v>0.186</v>
       </c>
       <c r="R15" t="n">
-        <v>0.089</v>
+        <v>0.129</v>
       </c>
       <c r="S15" t="n">
-        <v>0.049</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.023</v>
+        <v>0.046</v>
       </c>
       <c r="U15" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="V15" t="n">
         <v>0.002</v>
@@ -2279,138 +2247,138 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0.86</v>
       </c>
       <c r="C16" t="n">
-        <v>0.783</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.734</v>
+        <v>0.771</v>
       </c>
       <c r="E16" t="n">
-        <v>0.705</v>
+        <v>0.724</v>
       </c>
       <c r="F16" t="n">
-        <v>0.657</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.635</v>
+        <v>0.641</v>
       </c>
       <c r="H16" t="n">
-        <v>0.591</v>
+        <v>0.612</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.547</v>
       </c>
       <c r="J16" t="n">
-        <v>0.516</v>
+        <v>0.509</v>
       </c>
       <c r="K16" t="n">
-        <v>0.463</v>
+        <v>0.455</v>
       </c>
       <c r="L16" t="n">
-        <v>0.434</v>
+        <v>0.417</v>
       </c>
       <c r="M16" t="n">
-        <v>0.373</v>
+        <v>0.366</v>
       </c>
       <c r="N16" t="n">
-        <v>0.318</v>
+        <v>0.331</v>
       </c>
       <c r="O16" t="n">
-        <v>0.286</v>
+        <v>0.298</v>
       </c>
       <c r="P16" t="n">
-        <v>0.231</v>
+        <v>0.263</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.186</v>
+        <v>0.217</v>
       </c>
       <c r="R16" t="n">
-        <v>0.129</v>
+        <v>0.161</v>
       </c>
       <c r="S16" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.139</v>
       </c>
       <c r="T16" t="n">
-        <v>0.046</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.012</v>
+        <v>0.026</v>
       </c>
       <c r="V16" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>random_baseline</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0.86</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.618</v>
       </c>
       <c r="D17" t="n">
-        <v>0.771</v>
+        <v>0.545</v>
       </c>
       <c r="E17" t="n">
-        <v>0.724</v>
+        <v>0.459</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.398</v>
       </c>
       <c r="G17" t="n">
-        <v>0.641</v>
+        <v>0.328</v>
       </c>
       <c r="H17" t="n">
-        <v>0.612</v>
+        <v>0.273</v>
       </c>
       <c r="I17" t="n">
-        <v>0.547</v>
+        <v>0.22</v>
       </c>
       <c r="J17" t="n">
-        <v>0.509</v>
+        <v>0.169</v>
       </c>
       <c r="K17" t="n">
-        <v>0.455</v>
+        <v>0.134</v>
       </c>
       <c r="L17" t="n">
-        <v>0.417</v>
+        <v>0.101</v>
       </c>
       <c r="M17" t="n">
-        <v>0.366</v>
+        <v>0.076</v>
       </c>
       <c r="N17" t="n">
-        <v>0.331</v>
+        <v>0.055</v>
       </c>
       <c r="O17" t="n">
-        <v>0.298</v>
+        <v>0.035</v>
       </c>
       <c r="P17" t="n">
-        <v>0.263</v>
+        <v>0.027</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.217</v>
+        <v>0.017</v>
       </c>
       <c r="R17" t="n">
-        <v>0.161</v>
+        <v>0.008</v>
       </c>
       <c r="S17" t="n">
-        <v>0.139</v>
+        <v>0.003</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="U17" t="n">
-        <v>0.026</v>
+        <v>0.002</v>
       </c>
       <c r="V17" t="n">
         <v>0.001</v>
@@ -2419,68 +2387,68 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0.86</v>
       </c>
       <c r="C18" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.618</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.459</v>
-      </c>
       <c r="F18" t="n">
-        <v>0.398</v>
+        <v>0.574</v>
       </c>
       <c r="G18" t="n">
-        <v>0.328</v>
+        <v>0.521</v>
       </c>
       <c r="H18" t="n">
-        <v>0.273</v>
+        <v>0.488</v>
       </c>
       <c r="I18" t="n">
-        <v>0.22</v>
+        <v>0.43</v>
       </c>
       <c r="J18" t="n">
-        <v>0.169</v>
+        <v>0.386</v>
       </c>
       <c r="K18" t="n">
-        <v>0.134</v>
+        <v>0.355</v>
       </c>
       <c r="L18" t="n">
-        <v>0.101</v>
+        <v>0.309</v>
       </c>
       <c r="M18" t="n">
-        <v>0.076</v>
+        <v>0.266</v>
       </c>
       <c r="N18" t="n">
-        <v>0.055</v>
+        <v>0.227</v>
       </c>
       <c r="O18" t="n">
-        <v>0.035</v>
+        <v>0.194</v>
       </c>
       <c r="P18" t="n">
-        <v>0.027</v>
+        <v>0.131</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.017</v>
+        <v>0.095</v>
       </c>
       <c r="R18" t="n">
-        <v>0.008</v>
+        <v>0.064</v>
       </c>
       <c r="S18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="U18" t="n">
         <v>0.003</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.002</v>
       </c>
       <c r="V18" t="n">
         <v>0.001</v>
@@ -2489,210 +2457,140 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>sumDino</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0.86</v>
       </c>
       <c r="C19" t="n">
-        <v>0.743</v>
+        <v>0.831</v>
       </c>
       <c r="D19" t="n">
-        <v>0.671</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.618</v>
+        <v>0.8</v>
       </c>
       <c r="F19" t="n">
-        <v>0.574</v>
+        <v>0.773</v>
       </c>
       <c r="G19" t="n">
-        <v>0.521</v>
+        <v>0.758</v>
       </c>
       <c r="H19" t="n">
-        <v>0.488</v>
+        <v>0.721</v>
       </c>
       <c r="I19" t="n">
-        <v>0.43</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.386</v>
+        <v>0.653</v>
       </c>
       <c r="K19" t="n">
-        <v>0.355</v>
+        <v>0.591</v>
       </c>
       <c r="L19" t="n">
-        <v>0.309</v>
+        <v>0.535</v>
       </c>
       <c r="M19" t="n">
-        <v>0.266</v>
+        <v>0.494</v>
       </c>
       <c r="N19" t="n">
-        <v>0.227</v>
+        <v>0.46</v>
       </c>
       <c r="O19" t="n">
-        <v>0.194</v>
+        <v>0.396</v>
       </c>
       <c r="P19" t="n">
-        <v>0.131</v>
+        <v>0.346</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.095</v>
+        <v>0.291</v>
       </c>
       <c r="R19" t="n">
-        <v>0.064</v>
+        <v>0.233</v>
       </c>
       <c r="S19" t="n">
-        <v>0.03</v>
+        <v>0.179</v>
       </c>
       <c r="T19" t="n">
-        <v>0.016</v>
+        <v>0.101</v>
       </c>
       <c r="U19" t="n">
-        <v>0.003</v>
+        <v>0.04</v>
       </c>
       <c r="V19" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sumDino</t>
+          <t>xrai</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0.86</v>
       </c>
       <c r="C20" t="n">
-        <v>0.831</v>
+        <v>0.841</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8</v>
+        <v>0.781</v>
       </c>
       <c r="F20" t="n">
-        <v>0.773</v>
+        <v>0.763</v>
       </c>
       <c r="G20" t="n">
-        <v>0.758</v>
+        <v>0.73</v>
       </c>
       <c r="H20" t="n">
-        <v>0.721</v>
+        <v>0.698</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.656</v>
       </c>
       <c r="J20" t="n">
-        <v>0.653</v>
+        <v>0.603</v>
       </c>
       <c r="K20" t="n">
-        <v>0.591</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.535</v>
+        <v>0.504</v>
       </c>
       <c r="M20" t="n">
-        <v>0.494</v>
+        <v>0.455</v>
       </c>
       <c r="N20" t="n">
-        <v>0.46</v>
+        <v>0.398</v>
       </c>
       <c r="O20" t="n">
-        <v>0.396</v>
+        <v>0.35</v>
       </c>
       <c r="P20" t="n">
-        <v>0.346</v>
+        <v>0.293</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.291</v>
+        <v>0.225</v>
       </c>
       <c r="R20" t="n">
-        <v>0.233</v>
+        <v>0.155</v>
       </c>
       <c r="S20" t="n">
-        <v>0.179</v>
+        <v>0.103</v>
       </c>
       <c r="T20" t="n">
-        <v>0.101</v>
+        <v>0.059</v>
       </c>
       <c r="U20" t="n">
-        <v>0.04</v>
+        <v>0.019</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>xrai</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.841</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="V21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results/excel_reports/vgg16_resnet50_random_noise.xlsx
+++ b/results/excel_reports/vgg16_resnet50_random_noise.xlsx
@@ -1344,64 +1344,64 @@
         <v>0.86</v>
       </c>
       <c r="C3" t="n">
-        <v>0.842</v>
+        <v>0.841</v>
       </c>
       <c r="D3" t="n">
         <v>0.839</v>
       </c>
       <c r="E3" t="n">
-        <v>0.826</v>
+        <v>0.831</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.822</v>
       </c>
       <c r="G3" t="n">
-        <v>0.804</v>
+        <v>0.801</v>
       </c>
       <c r="H3" t="n">
-        <v>0.791</v>
+        <v>0.802</v>
       </c>
       <c r="I3" t="n">
-        <v>0.777</v>
+        <v>0.782</v>
       </c>
       <c r="J3" t="n">
-        <v>0.752</v>
+        <v>0.755</v>
       </c>
       <c r="K3" t="n">
         <v>0.725</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7</v>
+        <v>0.708</v>
       </c>
       <c r="M3" t="n">
-        <v>0.664</v>
+        <v>0.671</v>
       </c>
       <c r="N3" t="n">
-        <v>0.615</v>
+        <v>0.628</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.591</v>
       </c>
       <c r="P3" t="n">
-        <v>0.512</v>
+        <v>0.542</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.436</v>
+        <v>0.462</v>
       </c>
       <c r="R3" t="n">
-        <v>0.364</v>
+        <v>0.375</v>
       </c>
       <c r="S3" t="n">
-        <v>0.271</v>
+        <v>0.296</v>
       </c>
       <c r="T3" t="n">
-        <v>0.199</v>
+        <v>0.206</v>
       </c>
       <c r="U3" t="n">
-        <v>0.083</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="4">

--- a/results/excel_reports/vgg16_resnet50_random_noise.xlsx
+++ b/results/excel_reports/vgg16_resnet50_random_noise.xlsx
@@ -1344,7 +1344,7 @@
         <v>0.86</v>
       </c>
       <c r="C3" t="n">
-        <v>0.841</v>
+        <v>0.85</v>
       </c>
       <c r="D3" t="n">
         <v>0.839</v>
@@ -1353,52 +1353,52 @@
         <v>0.831</v>
       </c>
       <c r="F3" t="n">
-        <v>0.822</v>
+        <v>0.828</v>
       </c>
       <c r="G3" t="n">
-        <v>0.801</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.802</v>
+        <v>0.805</v>
       </c>
       <c r="I3" t="n">
-        <v>0.782</v>
+        <v>0.786</v>
       </c>
       <c r="J3" t="n">
-        <v>0.755</v>
+        <v>0.759</v>
       </c>
       <c r="K3" t="n">
-        <v>0.725</v>
+        <v>0.734</v>
       </c>
       <c r="L3" t="n">
-        <v>0.708</v>
+        <v>0.715</v>
       </c>
       <c r="M3" t="n">
-        <v>0.671</v>
+        <v>0.681</v>
       </c>
       <c r="N3" t="n">
-        <v>0.628</v>
+        <v>0.651</v>
       </c>
       <c r="O3" t="n">
-        <v>0.591</v>
+        <v>0.602</v>
       </c>
       <c r="P3" t="n">
-        <v>0.542</v>
+        <v>0.544</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.462</v>
+        <v>0.481</v>
       </c>
       <c r="R3" t="n">
-        <v>0.375</v>
+        <v>0.394</v>
       </c>
       <c r="S3" t="n">
-        <v>0.296</v>
+        <v>0.311</v>
       </c>
       <c r="T3" t="n">
-        <v>0.206</v>
+        <v>0.217</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0.002</v>

--- a/results/excel_reports/vgg16_resnet50_random_noise.xlsx
+++ b/results/excel_reports/vgg16_resnet50_random_noise.xlsx
@@ -784,6 +784,134 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="19"/>
+          <order val="19"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$21:$V$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="20"/>
+          <order val="20"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$22:$V$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="21"/>
+          <order val="21"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A23</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$23:$V$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="22"/>
+          <order val="22"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A24</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$24:$V$24</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -857,7 +985,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1167,10 +1295,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
@@ -1267,208 +1395,208 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>c3f</t>
+          <t>U2Net-Saliency</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0.86</v>
       </c>
       <c r="C2" t="n">
-        <v>0.847</v>
+        <v>0.841</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="E2" t="n">
-        <v>0.795</v>
+        <v>0.821</v>
       </c>
       <c r="F2" t="n">
-        <v>0.769</v>
+        <v>0.806</v>
       </c>
       <c r="G2" t="n">
-        <v>0.76</v>
+        <v>0.798</v>
       </c>
       <c r="H2" t="n">
-        <v>0.731</v>
+        <v>0.778</v>
       </c>
       <c r="I2" t="n">
-        <v>0.706</v>
+        <v>0.749</v>
       </c>
       <c r="J2" t="n">
-        <v>0.645</v>
+        <v>0.737</v>
       </c>
       <c r="K2" t="n">
-        <v>0.594</v>
+        <v>0.711</v>
       </c>
       <c r="L2" t="n">
-        <v>0.553</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.483</v>
+        <v>0.65</v>
       </c>
       <c r="N2" t="n">
-        <v>0.432</v>
+        <v>0.598</v>
       </c>
       <c r="O2" t="n">
-        <v>0.403</v>
+        <v>0.545</v>
       </c>
       <c r="P2" t="n">
-        <v>0.364</v>
+        <v>0.484</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.328</v>
+        <v>0.427</v>
       </c>
       <c r="R2" t="n">
-        <v>0.286</v>
+        <v>0.343</v>
       </c>
       <c r="S2" t="n">
-        <v>0.228</v>
+        <v>0.263</v>
       </c>
       <c r="T2" t="n">
-        <v>0.172</v>
+        <v>0.161</v>
       </c>
       <c r="U2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_ENT_SMOOTH</t>
+          <t>c3f</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.86</v>
       </c>
       <c r="C3" t="n">
-        <v>0.85</v>
+        <v>0.847</v>
       </c>
       <c r="D3" t="n">
-        <v>0.839</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.831</v>
+        <v>0.795</v>
       </c>
       <c r="F3" t="n">
-        <v>0.828</v>
+        <v>0.769</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="H3" t="n">
-        <v>0.805</v>
+        <v>0.731</v>
       </c>
       <c r="I3" t="n">
-        <v>0.786</v>
+        <v>0.706</v>
       </c>
       <c r="J3" t="n">
-        <v>0.759</v>
+        <v>0.645</v>
       </c>
       <c r="K3" t="n">
-        <v>0.734</v>
+        <v>0.594</v>
       </c>
       <c r="L3" t="n">
-        <v>0.715</v>
+        <v>0.553</v>
       </c>
       <c r="M3" t="n">
-        <v>0.681</v>
+        <v>0.483</v>
       </c>
       <c r="N3" t="n">
-        <v>0.651</v>
+        <v>0.432</v>
       </c>
       <c r="O3" t="n">
-        <v>0.602</v>
+        <v>0.403</v>
       </c>
       <c r="P3" t="n">
-        <v>0.544</v>
+        <v>0.364</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.481</v>
+        <v>0.328</v>
       </c>
       <c r="R3" t="n">
-        <v>0.394</v>
+        <v>0.286</v>
       </c>
       <c r="S3" t="n">
-        <v>0.311</v>
+        <v>0.228</v>
       </c>
       <c r="T3" t="n">
-        <v>0.217</v>
+        <v>0.172</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_FIXED</t>
+          <t>dinov2_COMBO_ENT_SMOOTH</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.86</v>
       </c>
       <c r="C4" t="n">
-        <v>0.836</v>
+        <v>0.851</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.843</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.832</v>
       </c>
       <c r="F4" t="n">
-        <v>0.782</v>
+        <v>0.819</v>
       </c>
       <c r="G4" t="n">
-        <v>0.776</v>
+        <v>0.806</v>
       </c>
       <c r="H4" t="n">
-        <v>0.759</v>
+        <v>0.795</v>
       </c>
       <c r="I4" t="n">
-        <v>0.735</v>
+        <v>0.78</v>
       </c>
       <c r="J4" t="n">
-        <v>0.699</v>
+        <v>0.764</v>
       </c>
       <c r="K4" t="n">
-        <v>0.666</v>
+        <v>0.737</v>
       </c>
       <c r="L4" t="n">
-        <v>0.633</v>
+        <v>0.713</v>
       </c>
       <c r="M4" t="n">
-        <v>0.585</v>
+        <v>0.681</v>
       </c>
       <c r="N4" t="n">
-        <v>0.533</v>
+        <v>0.636</v>
       </c>
       <c r="O4" t="n">
-        <v>0.488</v>
+        <v>0.581</v>
       </c>
       <c r="P4" t="n">
-        <v>0.414</v>
+        <v>0.544</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.338</v>
+        <v>0.47</v>
       </c>
       <c r="R4" t="n">
-        <v>0.274</v>
+        <v>0.398</v>
       </c>
       <c r="S4" t="n">
-        <v>0.187</v>
+        <v>0.306</v>
       </c>
       <c r="T4" t="n">
-        <v>0.098</v>
+        <v>0.204</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03</v>
+        <v>0.094</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1477,163 +1605,163 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dinov2_ENT</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.86</v>
       </c>
       <c r="C5" t="n">
-        <v>0.827</v>
+        <v>0.836</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.787</v>
+        <v>0.782</v>
       </c>
       <c r="G5" t="n">
-        <v>0.769</v>
+        <v>0.776</v>
       </c>
       <c r="H5" t="n">
-        <v>0.75</v>
+        <v>0.759</v>
       </c>
       <c r="I5" t="n">
-        <v>0.719</v>
+        <v>0.735</v>
       </c>
       <c r="J5" t="n">
-        <v>0.704</v>
+        <v>0.699</v>
       </c>
       <c r="K5" t="n">
         <v>0.666</v>
       </c>
       <c r="L5" t="n">
-        <v>0.619</v>
+        <v>0.633</v>
       </c>
       <c r="M5" t="n">
-        <v>0.578</v>
+        <v>0.585</v>
       </c>
       <c r="N5" t="n">
-        <v>0.528</v>
+        <v>0.533</v>
       </c>
       <c r="O5" t="n">
-        <v>0.491</v>
+        <v>0.488</v>
       </c>
       <c r="P5" t="n">
-        <v>0.415</v>
+        <v>0.414</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.355</v>
+        <v>0.338</v>
       </c>
       <c r="R5" t="n">
-        <v>0.281</v>
+        <v>0.274</v>
       </c>
       <c r="S5" t="n">
-        <v>0.207</v>
+        <v>0.187</v>
       </c>
       <c r="T5" t="n">
-        <v>0.123</v>
+        <v>0.098</v>
       </c>
       <c r="U5" t="n">
-        <v>0.051</v>
+        <v>0.03</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dinov2_PC1</t>
+          <t>dinov2_ENT</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.86</v>
       </c>
       <c r="C6" t="n">
-        <v>0.833</v>
+        <v>0.827</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.802</v>
+        <v>0.806</v>
       </c>
       <c r="F6" t="n">
-        <v>0.789</v>
+        <v>0.787</v>
       </c>
       <c r="G6" t="n">
-        <v>0.781</v>
+        <v>0.769</v>
       </c>
       <c r="H6" t="n">
-        <v>0.768</v>
+        <v>0.75</v>
       </c>
       <c r="I6" t="n">
-        <v>0.727</v>
+        <v>0.719</v>
       </c>
       <c r="J6" t="n">
-        <v>0.703</v>
+        <v>0.704</v>
       </c>
       <c r="K6" t="n">
-        <v>0.656</v>
+        <v>0.666</v>
       </c>
       <c r="L6" t="n">
-        <v>0.615</v>
+        <v>0.619</v>
       </c>
       <c r="M6" t="n">
-        <v>0.576</v>
+        <v>0.578</v>
       </c>
       <c r="N6" t="n">
-        <v>0.521</v>
+        <v>0.528</v>
       </c>
       <c r="O6" t="n">
-        <v>0.465</v>
+        <v>0.491</v>
       </c>
       <c r="P6" t="n">
-        <v>0.399</v>
+        <v>0.415</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.326</v>
+        <v>0.355</v>
       </c>
       <c r="R6" t="n">
-        <v>0.243</v>
+        <v>0.281</v>
       </c>
       <c r="S6" t="n">
-        <v>0.142</v>
+        <v>0.207</v>
       </c>
       <c r="T6" t="n">
-        <v>0.063</v>
+        <v>0.123</v>
       </c>
       <c r="U6" t="n">
-        <v>0.018</v>
+        <v>0.051</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dinov2_PC_EV</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.86</v>
       </c>
       <c r="C7" t="n">
-        <v>0.832</v>
+        <v>0.833</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.804</v>
+        <v>0.802</v>
       </c>
       <c r="F7" t="n">
-        <v>0.79</v>
+        <v>0.789</v>
       </c>
       <c r="G7" t="n">
         <v>0.781</v>
@@ -1642,43 +1770,43 @@
         <v>0.768</v>
       </c>
       <c r="I7" t="n">
-        <v>0.73</v>
+        <v>0.727</v>
       </c>
       <c r="J7" t="n">
-        <v>0.698</v>
+        <v>0.703</v>
       </c>
       <c r="K7" t="n">
-        <v>0.658</v>
+        <v>0.656</v>
       </c>
       <c r="L7" t="n">
-        <v>0.618</v>
+        <v>0.615</v>
       </c>
       <c r="M7" t="n">
-        <v>0.569</v>
+        <v>0.576</v>
       </c>
       <c r="N7" t="n">
-        <v>0.528</v>
+        <v>0.521</v>
       </c>
       <c r="O7" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="P7" t="n">
-        <v>0.389</v>
+        <v>0.399</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.324</v>
+        <v>0.326</v>
       </c>
       <c r="R7" t="n">
-        <v>0.24</v>
+        <v>0.243</v>
       </c>
       <c r="S7" t="n">
-        <v>0.136</v>
+        <v>0.142</v>
       </c>
       <c r="T7" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="U7" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="V7" t="n">
         <v>0.001</v>
@@ -1687,278 +1815,278 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dinov2_PC_L2</t>
+          <t>dinov2_PC_EV</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.86</v>
       </c>
       <c r="C8" t="n">
-        <v>0.791</v>
+        <v>0.832</v>
       </c>
       <c r="D8" t="n">
-        <v>0.755</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.723</v>
+        <v>0.804</v>
       </c>
       <c r="F8" t="n">
-        <v>0.677</v>
+        <v>0.79</v>
       </c>
       <c r="G8" t="n">
-        <v>0.62</v>
+        <v>0.781</v>
       </c>
       <c r="H8" t="n">
-        <v>0.572</v>
+        <v>0.768</v>
       </c>
       <c r="I8" t="n">
-        <v>0.523</v>
+        <v>0.73</v>
       </c>
       <c r="J8" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.464</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.247</v>
-      </c>
       <c r="P8" t="n">
-        <v>0.215</v>
+        <v>0.389</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.195</v>
+        <v>0.324</v>
       </c>
       <c r="R8" t="n">
-        <v>0.152</v>
+        <v>0.24</v>
       </c>
       <c r="S8" t="n">
-        <v>0.106</v>
+        <v>0.136</v>
       </c>
       <c r="T8" t="n">
-        <v>0.053</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>dinov2_PC_L2</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.86</v>
       </c>
       <c r="C9" t="n">
-        <v>0.821</v>
+        <v>0.791</v>
       </c>
       <c r="D9" t="n">
-        <v>0.798</v>
+        <v>0.755</v>
       </c>
       <c r="E9" t="n">
-        <v>0.775</v>
+        <v>0.723</v>
       </c>
       <c r="F9" t="n">
-        <v>0.756</v>
+        <v>0.677</v>
       </c>
       <c r="G9" t="n">
-        <v>0.732</v>
+        <v>0.62</v>
       </c>
       <c r="H9" t="n">
-        <v>0.705</v>
+        <v>0.572</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.523</v>
       </c>
       <c r="J9" t="n">
-        <v>0.635</v>
+        <v>0.464</v>
       </c>
       <c r="K9" t="n">
-        <v>0.614</v>
+        <v>0.41</v>
       </c>
       <c r="L9" t="n">
-        <v>0.571</v>
+        <v>0.357</v>
       </c>
       <c r="M9" t="n">
-        <v>0.524</v>
+        <v>0.317</v>
       </c>
       <c r="N9" t="n">
-        <v>0.486</v>
+        <v>0.278</v>
       </c>
       <c r="O9" t="n">
-        <v>0.435</v>
+        <v>0.247</v>
       </c>
       <c r="P9" t="n">
-        <v>0.374</v>
+        <v>0.215</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.322</v>
+        <v>0.195</v>
       </c>
       <c r="R9" t="n">
-        <v>0.258</v>
+        <v>0.152</v>
       </c>
       <c r="S9" t="n">
-        <v>0.186</v>
+        <v>0.106</v>
       </c>
       <c r="T9" t="n">
-        <v>0.12</v>
+        <v>0.053</v>
       </c>
       <c r="U9" t="n">
-        <v>0.049</v>
+        <v>0.021</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.86</v>
       </c>
       <c r="C10" t="n">
-        <v>0.795</v>
+        <v>0.821</v>
       </c>
       <c r="D10" t="n">
-        <v>0.751</v>
+        <v>0.798</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="F10" t="n">
-        <v>0.641</v>
+        <v>0.756</v>
       </c>
       <c r="G10" t="n">
-        <v>0.606</v>
+        <v>0.732</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.705</v>
       </c>
       <c r="I10" t="n">
-        <v>0.506</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.47</v>
+        <v>0.635</v>
       </c>
       <c r="K10" t="n">
-        <v>0.423</v>
+        <v>0.614</v>
       </c>
       <c r="L10" t="n">
-        <v>0.391</v>
+        <v>0.571</v>
       </c>
       <c r="M10" t="n">
-        <v>0.329</v>
+        <v>0.524</v>
       </c>
       <c r="N10" t="n">
-        <v>0.306</v>
+        <v>0.486</v>
       </c>
       <c r="O10" t="n">
-        <v>0.28</v>
+        <v>0.435</v>
       </c>
       <c r="P10" t="n">
-        <v>0.243</v>
+        <v>0.374</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.185</v>
+        <v>0.322</v>
       </c>
       <c r="R10" t="n">
-        <v>0.153</v>
+        <v>0.258</v>
       </c>
       <c r="S10" t="n">
-        <v>0.117</v>
+        <v>0.186</v>
       </c>
       <c r="T10" t="n">
-        <v>0.065</v>
+        <v>0.12</v>
       </c>
       <c r="U10" t="n">
-        <v>0.022</v>
+        <v>0.049</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.86</v>
       </c>
       <c r="C11" t="n">
-        <v>0.786</v>
+        <v>0.795</v>
       </c>
       <c r="D11" t="n">
-        <v>0.739</v>
+        <v>0.751</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.657</v>
+        <v>0.641</v>
       </c>
       <c r="G11" t="n">
-        <v>0.629</v>
+        <v>0.606</v>
       </c>
       <c r="H11" t="n">
-        <v>0.599</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.556</v>
+        <v>0.506</v>
       </c>
       <c r="J11" t="n">
-        <v>0.496</v>
+        <v>0.47</v>
       </c>
       <c r="K11" t="n">
-        <v>0.467</v>
+        <v>0.423</v>
       </c>
       <c r="L11" t="n">
-        <v>0.422</v>
+        <v>0.391</v>
       </c>
       <c r="M11" t="n">
-        <v>0.368</v>
+        <v>0.329</v>
       </c>
       <c r="N11" t="n">
-        <v>0.333</v>
+        <v>0.306</v>
       </c>
       <c r="O11" t="n">
-        <v>0.266</v>
+        <v>0.28</v>
       </c>
       <c r="P11" t="n">
-        <v>0.233</v>
+        <v>0.243</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.186</v>
+        <v>0.185</v>
       </c>
       <c r="R11" t="n">
-        <v>0.122</v>
+        <v>0.153</v>
       </c>
       <c r="S11" t="n">
-        <v>0.079</v>
+        <v>0.117</v>
       </c>
       <c r="T11" t="n">
-        <v>0.037</v>
+        <v>0.065</v>
       </c>
       <c r="U11" t="n">
-        <v>0.007</v>
+        <v>0.022</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1967,138 +2095,138 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.86</v>
       </c>
       <c r="C12" t="n">
-        <v>0.772</v>
+        <v>0.786</v>
       </c>
       <c r="D12" t="n">
-        <v>0.734</v>
+        <v>0.739</v>
       </c>
       <c r="E12" t="n">
-        <v>0.702</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.666</v>
+        <v>0.657</v>
       </c>
       <c r="G12" t="n">
-        <v>0.64</v>
+        <v>0.629</v>
       </c>
       <c r="H12" t="n">
-        <v>0.608</v>
+        <v>0.599</v>
       </c>
       <c r="I12" t="n">
-        <v>0.574</v>
+        <v>0.556</v>
       </c>
       <c r="J12" t="n">
-        <v>0.543</v>
+        <v>0.496</v>
       </c>
       <c r="K12" t="n">
-        <v>0.525</v>
+        <v>0.467</v>
       </c>
       <c r="L12" t="n">
-        <v>0.484</v>
+        <v>0.422</v>
       </c>
       <c r="M12" t="n">
-        <v>0.46</v>
+        <v>0.368</v>
       </c>
       <c r="N12" t="n">
-        <v>0.417</v>
+        <v>0.333</v>
       </c>
       <c r="O12" t="n">
-        <v>0.377</v>
+        <v>0.266</v>
       </c>
       <c r="P12" t="n">
-        <v>0.322</v>
+        <v>0.233</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.288</v>
+        <v>0.186</v>
       </c>
       <c r="R12" t="n">
-        <v>0.229</v>
+        <v>0.122</v>
       </c>
       <c r="S12" t="n">
-        <v>0.165</v>
+        <v>0.079</v>
       </c>
       <c r="T12" t="n">
-        <v>0.103</v>
+        <v>0.037</v>
       </c>
       <c r="U12" t="n">
-        <v>0.034</v>
+        <v>0.007</v>
       </c>
       <c r="V12" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.86</v>
       </c>
       <c r="C13" t="n">
-        <v>0.788</v>
+        <v>0.772</v>
       </c>
       <c r="D13" t="n">
-        <v>0.749</v>
+        <v>0.734</v>
       </c>
       <c r="E13" t="n">
-        <v>0.657</v>
+        <v>0.702</v>
       </c>
       <c r="F13" t="n">
-        <v>0.62</v>
+        <v>0.666</v>
       </c>
       <c r="G13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.574</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.543</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.451</v>
-      </c>
       <c r="K13" t="n">
-        <v>0.397</v>
+        <v>0.525</v>
       </c>
       <c r="L13" t="n">
-        <v>0.347</v>
+        <v>0.484</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="N13" t="n">
-        <v>0.264</v>
+        <v>0.417</v>
       </c>
       <c r="O13" t="n">
-        <v>0.234</v>
+        <v>0.377</v>
       </c>
       <c r="P13" t="n">
-        <v>0.195</v>
+        <v>0.322</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.148</v>
+        <v>0.288</v>
       </c>
       <c r="R13" t="n">
-        <v>0.114</v>
+        <v>0.229</v>
       </c>
       <c r="S13" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.165</v>
       </c>
       <c r="T13" t="n">
-        <v>0.04</v>
+        <v>0.103</v>
       </c>
       <c r="U13" t="n">
-        <v>0.017</v>
+        <v>0.034</v>
       </c>
       <c r="V13" t="n">
         <v>0.002</v>
@@ -2107,68 +2235,68 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.86</v>
       </c>
       <c r="C14" t="n">
-        <v>0.786</v>
+        <v>0.788</v>
       </c>
       <c r="D14" t="n">
-        <v>0.728</v>
+        <v>0.749</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.657</v>
       </c>
       <c r="F14" t="n">
-        <v>0.636</v>
+        <v>0.62</v>
       </c>
       <c r="G14" t="n">
-        <v>0.598</v>
+        <v>0.574</v>
       </c>
       <c r="H14" t="n">
-        <v>0.551</v>
+        <v>0.543</v>
       </c>
       <c r="I14" t="n">
-        <v>0.51</v>
+        <v>0.504</v>
       </c>
       <c r="J14" t="n">
-        <v>0.457</v>
+        <v>0.451</v>
       </c>
       <c r="K14" t="n">
-        <v>0.414</v>
+        <v>0.397</v>
       </c>
       <c r="L14" t="n">
-        <v>0.377</v>
+        <v>0.347</v>
       </c>
       <c r="M14" t="n">
-        <v>0.325</v>
+        <v>0.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.267</v>
+        <v>0.264</v>
       </c>
       <c r="O14" t="n">
-        <v>0.223</v>
+        <v>0.234</v>
       </c>
       <c r="P14" t="n">
-        <v>0.169</v>
+        <v>0.195</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.121</v>
+        <v>0.148</v>
       </c>
       <c r="R14" t="n">
-        <v>0.089</v>
+        <v>0.114</v>
       </c>
       <c r="S14" t="n">
-        <v>0.049</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.023</v>
+        <v>0.04</v>
       </c>
       <c r="U14" t="n">
-        <v>0.007</v>
+        <v>0.017</v>
       </c>
       <c r="V14" t="n">
         <v>0.002</v>
@@ -2177,68 +2305,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0.86</v>
       </c>
       <c r="C15" t="n">
-        <v>0.783</v>
+        <v>0.786</v>
       </c>
       <c r="D15" t="n">
-        <v>0.734</v>
+        <v>0.728</v>
       </c>
       <c r="E15" t="n">
-        <v>0.705</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.657</v>
+        <v>0.636</v>
       </c>
       <c r="G15" t="n">
-        <v>0.635</v>
+        <v>0.598</v>
       </c>
       <c r="H15" t="n">
-        <v>0.591</v>
+        <v>0.551</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="J15" t="n">
-        <v>0.516</v>
+        <v>0.457</v>
       </c>
       <c r="K15" t="n">
-        <v>0.463</v>
+        <v>0.414</v>
       </c>
       <c r="L15" t="n">
-        <v>0.434</v>
+        <v>0.377</v>
       </c>
       <c r="M15" t="n">
-        <v>0.373</v>
+        <v>0.325</v>
       </c>
       <c r="N15" t="n">
-        <v>0.318</v>
+        <v>0.267</v>
       </c>
       <c r="O15" t="n">
-        <v>0.286</v>
+        <v>0.223</v>
       </c>
       <c r="P15" t="n">
-        <v>0.231</v>
+        <v>0.169</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.186</v>
+        <v>0.121</v>
       </c>
       <c r="R15" t="n">
-        <v>0.129</v>
+        <v>0.089</v>
       </c>
       <c r="S15" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.049</v>
       </c>
       <c r="T15" t="n">
-        <v>0.046</v>
+        <v>0.023</v>
       </c>
       <c r="U15" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="V15" t="n">
         <v>0.002</v>
@@ -2247,350 +2375,630 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>inputxgradient_continuous</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0.86</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.837</v>
       </c>
       <c r="D16" t="n">
-        <v>0.771</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.724</v>
+        <v>0.784</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.754</v>
       </c>
       <c r="G16" t="n">
-        <v>0.641</v>
+        <v>0.726</v>
       </c>
       <c r="H16" t="n">
-        <v>0.612</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.547</v>
+        <v>0.627</v>
       </c>
       <c r="J16" t="n">
-        <v>0.509</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.455</v>
+        <v>0.507</v>
       </c>
       <c r="L16" t="n">
-        <v>0.417</v>
+        <v>0.462</v>
       </c>
       <c r="M16" t="n">
-        <v>0.366</v>
+        <v>0.394</v>
       </c>
       <c r="N16" t="n">
-        <v>0.331</v>
+        <v>0.337</v>
       </c>
       <c r="O16" t="n">
-        <v>0.298</v>
+        <v>0.279</v>
       </c>
       <c r="P16" t="n">
-        <v>0.263</v>
+        <v>0.222</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.217</v>
+        <v>0.163</v>
       </c>
       <c r="R16" t="n">
-        <v>0.161</v>
+        <v>0.118</v>
       </c>
       <c r="S16" t="n">
-        <v>0.139</v>
+        <v>0.074</v>
       </c>
       <c r="T16" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.046</v>
       </c>
       <c r="U16" t="n">
-        <v>0.026</v>
+        <v>0.012</v>
       </c>
       <c r="V16" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>inputxgradient_u2net_fill</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0.86</v>
       </c>
       <c r="C17" t="n">
-        <v>0.618</v>
+        <v>0.821</v>
       </c>
       <c r="D17" t="n">
-        <v>0.545</v>
+        <v>0.801</v>
       </c>
       <c r="E17" t="n">
-        <v>0.459</v>
+        <v>0.794</v>
       </c>
       <c r="F17" t="n">
-        <v>0.398</v>
+        <v>0.767</v>
       </c>
       <c r="G17" t="n">
-        <v>0.328</v>
+        <v>0.748</v>
       </c>
       <c r="H17" t="n">
-        <v>0.273</v>
+        <v>0.721</v>
       </c>
       <c r="I17" t="n">
-        <v>0.22</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.169</v>
+        <v>0.659</v>
       </c>
       <c r="K17" t="n">
-        <v>0.134</v>
+        <v>0.635</v>
       </c>
       <c r="L17" t="n">
-        <v>0.101</v>
+        <v>0.608</v>
       </c>
       <c r="M17" t="n">
-        <v>0.076</v>
+        <v>0.573</v>
       </c>
       <c r="N17" t="n">
-        <v>0.055</v>
+        <v>0.544</v>
       </c>
       <c r="O17" t="n">
-        <v>0.035</v>
+        <v>0.51</v>
       </c>
       <c r="P17" t="n">
-        <v>0.027</v>
+        <v>0.466</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.017</v>
+        <v>0.42</v>
       </c>
       <c r="R17" t="n">
-        <v>0.008</v>
+        <v>0.348</v>
       </c>
       <c r="S17" t="n">
-        <v>0.003</v>
+        <v>0.263</v>
       </c>
       <c r="T17" t="n">
-        <v>0.003</v>
+        <v>0.165</v>
       </c>
       <c r="U17" t="n">
-        <v>0.002</v>
+        <v>0.061</v>
       </c>
       <c r="V17" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0.86</v>
       </c>
       <c r="C18" t="n">
-        <v>0.743</v>
+        <v>0.783</v>
       </c>
       <c r="D18" t="n">
-        <v>0.671</v>
+        <v>0.734</v>
       </c>
       <c r="E18" t="n">
-        <v>0.618</v>
+        <v>0.705</v>
       </c>
       <c r="F18" t="n">
-        <v>0.574</v>
+        <v>0.657</v>
       </c>
       <c r="G18" t="n">
-        <v>0.521</v>
+        <v>0.635</v>
       </c>
       <c r="H18" t="n">
-        <v>0.488</v>
+        <v>0.591</v>
       </c>
       <c r="I18" t="n">
-        <v>0.43</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.386</v>
+        <v>0.516</v>
       </c>
       <c r="K18" t="n">
-        <v>0.355</v>
+        <v>0.463</v>
       </c>
       <c r="L18" t="n">
-        <v>0.309</v>
+        <v>0.434</v>
       </c>
       <c r="M18" t="n">
-        <v>0.266</v>
+        <v>0.373</v>
       </c>
       <c r="N18" t="n">
-        <v>0.227</v>
+        <v>0.318</v>
       </c>
       <c r="O18" t="n">
-        <v>0.194</v>
+        <v>0.286</v>
       </c>
       <c r="P18" t="n">
-        <v>0.131</v>
+        <v>0.231</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.095</v>
+        <v>0.186</v>
       </c>
       <c r="R18" t="n">
-        <v>0.064</v>
+        <v>0.129</v>
       </c>
       <c r="S18" t="n">
-        <v>0.03</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.016</v>
+        <v>0.046</v>
       </c>
       <c r="U18" t="n">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="V18" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sumDino</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0.86</v>
       </c>
       <c r="C19" t="n">
-        <v>0.831</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.771</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8</v>
+        <v>0.724</v>
       </c>
       <c r="F19" t="n">
-        <v>0.773</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.758</v>
+        <v>0.641</v>
       </c>
       <c r="H19" t="n">
-        <v>0.721</v>
+        <v>0.612</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.547</v>
       </c>
       <c r="J19" t="n">
-        <v>0.653</v>
+        <v>0.509</v>
       </c>
       <c r="K19" t="n">
-        <v>0.591</v>
+        <v>0.455</v>
       </c>
       <c r="L19" t="n">
-        <v>0.535</v>
+        <v>0.417</v>
       </c>
       <c r="M19" t="n">
-        <v>0.494</v>
+        <v>0.366</v>
       </c>
       <c r="N19" t="n">
-        <v>0.46</v>
+        <v>0.331</v>
       </c>
       <c r="O19" t="n">
-        <v>0.396</v>
+        <v>0.298</v>
       </c>
       <c r="P19" t="n">
-        <v>0.346</v>
+        <v>0.263</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.291</v>
+        <v>0.217</v>
       </c>
       <c r="R19" t="n">
-        <v>0.233</v>
+        <v>0.161</v>
       </c>
       <c r="S19" t="n">
-        <v>0.179</v>
+        <v>0.139</v>
       </c>
       <c r="T19" t="n">
-        <v>0.101</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.04</v>
+        <v>0.026</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>random_baseline</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>saliency</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sumDino</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>u2net_dino_fusion</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>xrai</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B24" t="n">
         <v>0.86</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C24" t="n">
         <v>0.841</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D24" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E24" t="n">
         <v>0.781</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F24" t="n">
         <v>0.763</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G24" t="n">
         <v>0.73</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H24" t="n">
         <v>0.698</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I24" t="n">
         <v>0.656</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J24" t="n">
         <v>0.603</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K24" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L24" t="n">
         <v>0.504</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M24" t="n">
         <v>0.455</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N24" t="n">
         <v>0.398</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O24" t="n">
         <v>0.35</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P24" t="n">
         <v>0.293</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q24" t="n">
         <v>0.225</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R24" t="n">
         <v>0.155</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S24" t="n">
         <v>0.103</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T24" t="n">
         <v>0.059</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U24" t="n">
         <v>0.019</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V24" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results/excel_reports/vgg16_resnet50_random_noise.xlsx
+++ b/results/excel_reports/vgg16_resnet50_random_noise.xlsx
@@ -752,166 +752,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="18"/>
-          <order val="18"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A20</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$20:$V$20</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="19"/>
-          <order val="19"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$21:$V$21</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="20"/>
-          <order val="20"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$22:$V$22</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="21"/>
-          <order val="21"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A23</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$23:$V$23</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="22"/>
-          <order val="22"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A24</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$24:$V$24</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -985,7 +825,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1295,7 +1135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1395,68 +1235,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>U2Net-Saliency</t>
+          <t>random_baseline</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0.86</v>
       </c>
       <c r="C2" t="n">
-        <v>0.841</v>
+        <v>0.618</v>
       </c>
       <c r="D2" t="n">
-        <v>0.833</v>
+        <v>0.545</v>
       </c>
       <c r="E2" t="n">
-        <v>0.821</v>
+        <v>0.459</v>
       </c>
       <c r="F2" t="n">
-        <v>0.806</v>
+        <v>0.398</v>
       </c>
       <c r="G2" t="n">
-        <v>0.798</v>
+        <v>0.328</v>
       </c>
       <c r="H2" t="n">
-        <v>0.778</v>
+        <v>0.273</v>
       </c>
       <c r="I2" t="n">
-        <v>0.749</v>
+        <v>0.22</v>
       </c>
       <c r="J2" t="n">
-        <v>0.737</v>
+        <v>0.169</v>
       </c>
       <c r="K2" t="n">
-        <v>0.711</v>
+        <v>0.134</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="M2" t="n">
-        <v>0.65</v>
+        <v>0.076</v>
       </c>
       <c r="N2" t="n">
-        <v>0.598</v>
+        <v>0.055</v>
       </c>
       <c r="O2" t="n">
-        <v>0.545</v>
+        <v>0.035</v>
       </c>
       <c r="P2" t="n">
-        <v>0.484</v>
+        <v>0.027</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.427</v>
+        <v>0.017</v>
       </c>
       <c r="R2" t="n">
-        <v>0.343</v>
+        <v>0.008</v>
       </c>
       <c r="S2" t="n">
-        <v>0.263</v>
+        <v>0.003</v>
       </c>
       <c r="T2" t="n">
-        <v>0.161</v>
+        <v>0.003</v>
       </c>
       <c r="U2" t="n">
-        <v>0.066</v>
+        <v>0.002</v>
       </c>
       <c r="V2" t="n">
         <v>0.001</v>
@@ -1465,558 +1305,558 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>c3f</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.86</v>
       </c>
       <c r="C3" t="n">
-        <v>0.847</v>
+        <v>0.743</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.671</v>
       </c>
       <c r="E3" t="n">
-        <v>0.795</v>
+        <v>0.618</v>
       </c>
       <c r="F3" t="n">
-        <v>0.769</v>
+        <v>0.574</v>
       </c>
       <c r="G3" t="n">
-        <v>0.76</v>
+        <v>0.521</v>
       </c>
       <c r="H3" t="n">
-        <v>0.731</v>
+        <v>0.488</v>
       </c>
       <c r="I3" t="n">
-        <v>0.706</v>
+        <v>0.43</v>
       </c>
       <c r="J3" t="n">
-        <v>0.645</v>
+        <v>0.386</v>
       </c>
       <c r="K3" t="n">
-        <v>0.594</v>
+        <v>0.355</v>
       </c>
       <c r="L3" t="n">
-        <v>0.553</v>
+        <v>0.309</v>
       </c>
       <c r="M3" t="n">
-        <v>0.483</v>
+        <v>0.266</v>
       </c>
       <c r="N3" t="n">
-        <v>0.432</v>
+        <v>0.227</v>
       </c>
       <c r="O3" t="n">
-        <v>0.403</v>
+        <v>0.194</v>
       </c>
       <c r="P3" t="n">
-        <v>0.364</v>
+        <v>0.131</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.328</v>
+        <v>0.095</v>
       </c>
       <c r="R3" t="n">
-        <v>0.286</v>
+        <v>0.064</v>
       </c>
       <c r="S3" t="n">
-        <v>0.228</v>
+        <v>0.03</v>
       </c>
       <c r="T3" t="n">
-        <v>0.172</v>
+        <v>0.016</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.003</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_ENT_SMOOTH</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.86</v>
       </c>
       <c r="C4" t="n">
-        <v>0.851</v>
+        <v>0.786</v>
       </c>
       <c r="D4" t="n">
-        <v>0.843</v>
+        <v>0.728</v>
       </c>
       <c r="E4" t="n">
-        <v>0.832</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.819</v>
+        <v>0.636</v>
       </c>
       <c r="G4" t="n">
-        <v>0.806</v>
+        <v>0.598</v>
       </c>
       <c r="H4" t="n">
-        <v>0.795</v>
+        <v>0.551</v>
       </c>
       <c r="I4" t="n">
-        <v>0.78</v>
+        <v>0.51</v>
       </c>
       <c r="J4" t="n">
-        <v>0.764</v>
+        <v>0.457</v>
       </c>
       <c r="K4" t="n">
-        <v>0.737</v>
+        <v>0.414</v>
       </c>
       <c r="L4" t="n">
-        <v>0.713</v>
+        <v>0.377</v>
       </c>
       <c r="M4" t="n">
-        <v>0.681</v>
+        <v>0.325</v>
       </c>
       <c r="N4" t="n">
-        <v>0.636</v>
+        <v>0.267</v>
       </c>
       <c r="O4" t="n">
-        <v>0.581</v>
+        <v>0.223</v>
       </c>
       <c r="P4" t="n">
-        <v>0.544</v>
+        <v>0.169</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.47</v>
+        <v>0.121</v>
       </c>
       <c r="R4" t="n">
-        <v>0.398</v>
+        <v>0.089</v>
       </c>
       <c r="S4" t="n">
-        <v>0.306</v>
+        <v>0.049</v>
       </c>
       <c r="T4" t="n">
-        <v>0.204</v>
+        <v>0.023</v>
       </c>
       <c r="U4" t="n">
-        <v>0.094</v>
+        <v>0.007</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_FIXED</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.86</v>
       </c>
       <c r="C5" t="n">
-        <v>0.836</v>
+        <v>0.788</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.749</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.657</v>
       </c>
       <c r="F5" t="n">
-        <v>0.782</v>
+        <v>0.62</v>
       </c>
       <c r="G5" t="n">
-        <v>0.776</v>
+        <v>0.574</v>
       </c>
       <c r="H5" t="n">
-        <v>0.759</v>
+        <v>0.543</v>
       </c>
       <c r="I5" t="n">
-        <v>0.735</v>
+        <v>0.504</v>
       </c>
       <c r="J5" t="n">
-        <v>0.699</v>
+        <v>0.451</v>
       </c>
       <c r="K5" t="n">
-        <v>0.666</v>
+        <v>0.397</v>
       </c>
       <c r="L5" t="n">
-        <v>0.633</v>
+        <v>0.347</v>
       </c>
       <c r="M5" t="n">
-        <v>0.585</v>
+        <v>0.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.533</v>
+        <v>0.264</v>
       </c>
       <c r="O5" t="n">
-        <v>0.488</v>
+        <v>0.234</v>
       </c>
       <c r="P5" t="n">
-        <v>0.414</v>
+        <v>0.195</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.338</v>
+        <v>0.148</v>
       </c>
       <c r="R5" t="n">
-        <v>0.274</v>
+        <v>0.114</v>
       </c>
       <c r="S5" t="n">
-        <v>0.187</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.098</v>
+        <v>0.04</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dinov2_ENT</t>
+          <t>inputxgradient_continuous</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.86</v>
       </c>
       <c r="C6" t="n">
-        <v>0.827</v>
+        <v>0.837</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.806</v>
+        <v>0.784</v>
       </c>
       <c r="F6" t="n">
-        <v>0.787</v>
+        <v>0.754</v>
       </c>
       <c r="G6" t="n">
-        <v>0.769</v>
+        <v>0.726</v>
       </c>
       <c r="H6" t="n">
-        <v>0.75</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.719</v>
+        <v>0.627</v>
       </c>
       <c r="J6" t="n">
-        <v>0.704</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.666</v>
+        <v>0.507</v>
       </c>
       <c r="L6" t="n">
-        <v>0.619</v>
+        <v>0.462</v>
       </c>
       <c r="M6" t="n">
-        <v>0.578</v>
+        <v>0.394</v>
       </c>
       <c r="N6" t="n">
-        <v>0.528</v>
+        <v>0.337</v>
       </c>
       <c r="O6" t="n">
-        <v>0.491</v>
+        <v>0.279</v>
       </c>
       <c r="P6" t="n">
-        <v>0.415</v>
+        <v>0.222</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.355</v>
+        <v>0.163</v>
       </c>
       <c r="R6" t="n">
-        <v>0.281</v>
+        <v>0.118</v>
       </c>
       <c r="S6" t="n">
-        <v>0.207</v>
+        <v>0.074</v>
       </c>
       <c r="T6" t="n">
-        <v>0.123</v>
+        <v>0.046</v>
       </c>
       <c r="U6" t="n">
-        <v>0.051</v>
+        <v>0.012</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dinov2_PC1</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.86</v>
       </c>
       <c r="C7" t="n">
-        <v>0.833</v>
+        <v>0.795</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.751</v>
       </c>
       <c r="E7" t="n">
-        <v>0.802</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.789</v>
+        <v>0.641</v>
       </c>
       <c r="G7" t="n">
-        <v>0.781</v>
+        <v>0.606</v>
       </c>
       <c r="H7" t="n">
-        <v>0.768</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.727</v>
+        <v>0.506</v>
       </c>
       <c r="J7" t="n">
-        <v>0.703</v>
+        <v>0.47</v>
       </c>
       <c r="K7" t="n">
-        <v>0.656</v>
+        <v>0.423</v>
       </c>
       <c r="L7" t="n">
-        <v>0.615</v>
+        <v>0.391</v>
       </c>
       <c r="M7" t="n">
-        <v>0.576</v>
+        <v>0.329</v>
       </c>
       <c r="N7" t="n">
-        <v>0.521</v>
+        <v>0.306</v>
       </c>
       <c r="O7" t="n">
-        <v>0.465</v>
+        <v>0.28</v>
       </c>
       <c r="P7" t="n">
-        <v>0.399</v>
+        <v>0.243</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.326</v>
+        <v>0.185</v>
       </c>
       <c r="R7" t="n">
-        <v>0.243</v>
+        <v>0.153</v>
       </c>
       <c r="S7" t="n">
-        <v>0.142</v>
+        <v>0.117</v>
       </c>
       <c r="T7" t="n">
-        <v>0.063</v>
+        <v>0.065</v>
       </c>
       <c r="U7" t="n">
-        <v>0.018</v>
+        <v>0.022</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dinov2_PC_EV</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.86</v>
       </c>
       <c r="C8" t="n">
-        <v>0.832</v>
+        <v>0.786</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.739</v>
       </c>
       <c r="E8" t="n">
-        <v>0.804</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.79</v>
+        <v>0.657</v>
       </c>
       <c r="G8" t="n">
-        <v>0.781</v>
+        <v>0.629</v>
       </c>
       <c r="H8" t="n">
-        <v>0.768</v>
+        <v>0.599</v>
       </c>
       <c r="I8" t="n">
-        <v>0.73</v>
+        <v>0.556</v>
       </c>
       <c r="J8" t="n">
-        <v>0.698</v>
+        <v>0.496</v>
       </c>
       <c r="K8" t="n">
-        <v>0.658</v>
+        <v>0.467</v>
       </c>
       <c r="L8" t="n">
-        <v>0.618</v>
+        <v>0.422</v>
       </c>
       <c r="M8" t="n">
-        <v>0.569</v>
+        <v>0.368</v>
       </c>
       <c r="N8" t="n">
-        <v>0.528</v>
+        <v>0.333</v>
       </c>
       <c r="O8" t="n">
-        <v>0.464</v>
+        <v>0.266</v>
       </c>
       <c r="P8" t="n">
-        <v>0.389</v>
+        <v>0.233</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.324</v>
+        <v>0.186</v>
       </c>
       <c r="R8" t="n">
-        <v>0.24</v>
+        <v>0.122</v>
       </c>
       <c r="S8" t="n">
-        <v>0.136</v>
+        <v>0.079</v>
       </c>
       <c r="T8" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.037</v>
       </c>
       <c r="U8" t="n">
-        <v>0.019</v>
+        <v>0.007</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dinov2_PC_L2</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.86</v>
       </c>
       <c r="C9" t="n">
-        <v>0.791</v>
+        <v>0.783</v>
       </c>
       <c r="D9" t="n">
-        <v>0.755</v>
+        <v>0.734</v>
       </c>
       <c r="E9" t="n">
-        <v>0.723</v>
+        <v>0.705</v>
       </c>
       <c r="F9" t="n">
-        <v>0.677</v>
+        <v>0.657</v>
       </c>
       <c r="G9" t="n">
-        <v>0.62</v>
+        <v>0.635</v>
       </c>
       <c r="H9" t="n">
-        <v>0.572</v>
+        <v>0.591</v>
       </c>
       <c r="I9" t="n">
-        <v>0.523</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.464</v>
+        <v>0.516</v>
       </c>
       <c r="K9" t="n">
-        <v>0.41</v>
+        <v>0.463</v>
       </c>
       <c r="L9" t="n">
-        <v>0.357</v>
+        <v>0.434</v>
       </c>
       <c r="M9" t="n">
-        <v>0.317</v>
+        <v>0.373</v>
       </c>
       <c r="N9" t="n">
-        <v>0.278</v>
+        <v>0.318</v>
       </c>
       <c r="O9" t="n">
-        <v>0.247</v>
+        <v>0.286</v>
       </c>
       <c r="P9" t="n">
-        <v>0.215</v>
+        <v>0.231</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.195</v>
+        <v>0.186</v>
       </c>
       <c r="R9" t="n">
-        <v>0.152</v>
+        <v>0.129</v>
       </c>
       <c r="S9" t="n">
-        <v>0.106</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.053</v>
+        <v>0.046</v>
       </c>
       <c r="U9" t="n">
-        <v>0.021</v>
+        <v>0.012</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.86</v>
       </c>
       <c r="C10" t="n">
-        <v>0.821</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.798</v>
+        <v>0.771</v>
       </c>
       <c r="E10" t="n">
-        <v>0.775</v>
+        <v>0.724</v>
       </c>
       <c r="F10" t="n">
-        <v>0.756</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.732</v>
+        <v>0.641</v>
       </c>
       <c r="H10" t="n">
-        <v>0.705</v>
+        <v>0.612</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.547</v>
       </c>
       <c r="J10" t="n">
-        <v>0.635</v>
+        <v>0.509</v>
       </c>
       <c r="K10" t="n">
-        <v>0.614</v>
+        <v>0.455</v>
       </c>
       <c r="L10" t="n">
-        <v>0.571</v>
+        <v>0.417</v>
       </c>
       <c r="M10" t="n">
-        <v>0.524</v>
+        <v>0.366</v>
       </c>
       <c r="N10" t="n">
-        <v>0.486</v>
+        <v>0.331</v>
       </c>
       <c r="O10" t="n">
-        <v>0.435</v>
+        <v>0.298</v>
       </c>
       <c r="P10" t="n">
-        <v>0.374</v>
+        <v>0.263</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.322</v>
+        <v>0.217</v>
       </c>
       <c r="R10" t="n">
-        <v>0.258</v>
+        <v>0.161</v>
       </c>
       <c r="S10" t="n">
-        <v>0.186</v>
+        <v>0.139</v>
       </c>
       <c r="T10" t="n">
-        <v>0.12</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.049</v>
+        <v>0.026</v>
       </c>
       <c r="V10" t="n">
         <v>0.001</v>
@@ -2025,68 +1865,68 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>xrai</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.86</v>
       </c>
       <c r="C11" t="n">
-        <v>0.795</v>
+        <v>0.841</v>
       </c>
       <c r="D11" t="n">
-        <v>0.751</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.781</v>
       </c>
       <c r="F11" t="n">
-        <v>0.641</v>
+        <v>0.763</v>
       </c>
       <c r="G11" t="n">
-        <v>0.606</v>
+        <v>0.73</v>
       </c>
       <c r="H11" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.423</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.391</v>
+        <v>0.504</v>
       </c>
       <c r="M11" t="n">
-        <v>0.329</v>
+        <v>0.455</v>
       </c>
       <c r="N11" t="n">
-        <v>0.306</v>
+        <v>0.398</v>
       </c>
       <c r="O11" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="P11" t="n">
-        <v>0.243</v>
+        <v>0.293</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.185</v>
+        <v>0.225</v>
       </c>
       <c r="R11" t="n">
-        <v>0.153</v>
+        <v>0.155</v>
       </c>
       <c r="S11" t="n">
-        <v>0.117</v>
+        <v>0.103</v>
       </c>
       <c r="T11" t="n">
-        <v>0.065</v>
+        <v>0.059</v>
       </c>
       <c r="U11" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2095,418 +1935,418 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.86</v>
       </c>
       <c r="C12" t="n">
-        <v>0.786</v>
+        <v>0.772</v>
       </c>
       <c r="D12" t="n">
-        <v>0.739</v>
+        <v>0.734</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.702</v>
       </c>
       <c r="F12" t="n">
-        <v>0.657</v>
+        <v>0.666</v>
       </c>
       <c r="G12" t="n">
-        <v>0.629</v>
+        <v>0.64</v>
       </c>
       <c r="H12" t="n">
-        <v>0.599</v>
+        <v>0.608</v>
       </c>
       <c r="I12" t="n">
-        <v>0.556</v>
+        <v>0.574</v>
       </c>
       <c r="J12" t="n">
-        <v>0.496</v>
+        <v>0.543</v>
       </c>
       <c r="K12" t="n">
-        <v>0.467</v>
+        <v>0.525</v>
       </c>
       <c r="L12" t="n">
-        <v>0.422</v>
+        <v>0.484</v>
       </c>
       <c r="M12" t="n">
-        <v>0.368</v>
+        <v>0.46</v>
       </c>
       <c r="N12" t="n">
-        <v>0.333</v>
+        <v>0.417</v>
       </c>
       <c r="O12" t="n">
-        <v>0.266</v>
+        <v>0.377</v>
       </c>
       <c r="P12" t="n">
-        <v>0.233</v>
+        <v>0.322</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.186</v>
+        <v>0.288</v>
       </c>
       <c r="R12" t="n">
-        <v>0.122</v>
+        <v>0.229</v>
       </c>
       <c r="S12" t="n">
-        <v>0.079</v>
+        <v>0.165</v>
       </c>
       <c r="T12" t="n">
-        <v>0.037</v>
+        <v>0.103</v>
       </c>
       <c r="U12" t="n">
-        <v>0.007</v>
+        <v>0.034</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.86</v>
       </c>
       <c r="C13" t="n">
-        <v>0.772</v>
+        <v>0.821</v>
       </c>
       <c r="D13" t="n">
-        <v>0.734</v>
+        <v>0.798</v>
       </c>
       <c r="E13" t="n">
-        <v>0.702</v>
+        <v>0.775</v>
       </c>
       <c r="F13" t="n">
-        <v>0.666</v>
+        <v>0.756</v>
       </c>
       <c r="G13" t="n">
-        <v>0.64</v>
+        <v>0.732</v>
       </c>
       <c r="H13" t="n">
-        <v>0.608</v>
+        <v>0.705</v>
       </c>
       <c r="I13" t="n">
-        <v>0.574</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.543</v>
+        <v>0.635</v>
       </c>
       <c r="K13" t="n">
-        <v>0.525</v>
+        <v>0.614</v>
       </c>
       <c r="L13" t="n">
-        <v>0.484</v>
+        <v>0.571</v>
       </c>
       <c r="M13" t="n">
-        <v>0.46</v>
+        <v>0.524</v>
       </c>
       <c r="N13" t="n">
-        <v>0.417</v>
+        <v>0.486</v>
       </c>
       <c r="O13" t="n">
-        <v>0.377</v>
+        <v>0.435</v>
       </c>
       <c r="P13" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0.322</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0.288</v>
-      </c>
       <c r="R13" t="n">
-        <v>0.229</v>
+        <v>0.258</v>
       </c>
       <c r="S13" t="n">
-        <v>0.165</v>
+        <v>0.186</v>
       </c>
       <c r="T13" t="n">
-        <v>0.103</v>
+        <v>0.12</v>
       </c>
       <c r="U13" t="n">
-        <v>0.034</v>
+        <v>0.049</v>
       </c>
       <c r="V13" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.86</v>
       </c>
       <c r="C14" t="n">
-        <v>0.788</v>
+        <v>0.833</v>
       </c>
       <c r="D14" t="n">
-        <v>0.749</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.657</v>
+        <v>0.802</v>
       </c>
       <c r="F14" t="n">
-        <v>0.62</v>
+        <v>0.789</v>
       </c>
       <c r="G14" t="n">
-        <v>0.574</v>
+        <v>0.781</v>
       </c>
       <c r="H14" t="n">
-        <v>0.543</v>
+        <v>0.768</v>
       </c>
       <c r="I14" t="n">
-        <v>0.504</v>
+        <v>0.727</v>
       </c>
       <c r="J14" t="n">
-        <v>0.451</v>
+        <v>0.703</v>
       </c>
       <c r="K14" t="n">
-        <v>0.397</v>
+        <v>0.656</v>
       </c>
       <c r="L14" t="n">
-        <v>0.347</v>
+        <v>0.615</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3</v>
+        <v>0.576</v>
       </c>
       <c r="N14" t="n">
-        <v>0.264</v>
+        <v>0.521</v>
       </c>
       <c r="O14" t="n">
-        <v>0.234</v>
+        <v>0.465</v>
       </c>
       <c r="P14" t="n">
-        <v>0.195</v>
+        <v>0.399</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.148</v>
+        <v>0.326</v>
       </c>
       <c r="R14" t="n">
-        <v>0.114</v>
+        <v>0.243</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="T14" t="n">
-        <v>0.04</v>
+        <v>0.063</v>
       </c>
       <c r="U14" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="V14" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0.86</v>
       </c>
       <c r="C15" t="n">
-        <v>0.786</v>
+        <v>0.836</v>
       </c>
       <c r="D15" t="n">
-        <v>0.728</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.636</v>
+        <v>0.782</v>
       </c>
       <c r="G15" t="n">
-        <v>0.598</v>
+        <v>0.776</v>
       </c>
       <c r="H15" t="n">
-        <v>0.551</v>
+        <v>0.759</v>
       </c>
       <c r="I15" t="n">
-        <v>0.51</v>
+        <v>0.735</v>
       </c>
       <c r="J15" t="n">
-        <v>0.457</v>
+        <v>0.699</v>
       </c>
       <c r="K15" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="P15" t="n">
         <v>0.414</v>
       </c>
-      <c r="L15" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.169</v>
-      </c>
       <c r="Q15" t="n">
-        <v>0.121</v>
+        <v>0.338</v>
       </c>
       <c r="R15" t="n">
-        <v>0.089</v>
+        <v>0.274</v>
       </c>
       <c r="S15" t="n">
-        <v>0.049</v>
+        <v>0.187</v>
       </c>
       <c r="T15" t="n">
-        <v>0.023</v>
+        <v>0.098</v>
       </c>
       <c r="U15" t="n">
-        <v>0.007</v>
+        <v>0.03</v>
       </c>
       <c r="V15" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inputxgradient_continuous</t>
+          <t>u2net_dino_fusion</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0.86</v>
       </c>
       <c r="C16" t="n">
-        <v>0.837</v>
+        <v>0.843</v>
       </c>
       <c r="D16" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="E16" t="n">
         <v>0.8080000000000001</v>
       </c>
-      <c r="E16" t="n">
-        <v>0.784</v>
-      </c>
       <c r="F16" t="n">
-        <v>0.754</v>
+        <v>0.796</v>
       </c>
       <c r="G16" t="n">
-        <v>0.726</v>
+        <v>0.785</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.771</v>
       </c>
       <c r="I16" t="n">
-        <v>0.627</v>
+        <v>0.739</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="K16" t="n">
-        <v>0.507</v>
+        <v>0.679</v>
       </c>
       <c r="L16" t="n">
-        <v>0.462</v>
+        <v>0.648</v>
       </c>
       <c r="M16" t="n">
-        <v>0.394</v>
+        <v>0.616</v>
       </c>
       <c r="N16" t="n">
-        <v>0.337</v>
+        <v>0.57</v>
       </c>
       <c r="O16" t="n">
-        <v>0.279</v>
+        <v>0.51</v>
       </c>
       <c r="P16" t="n">
-        <v>0.222</v>
+        <v>0.456</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.163</v>
+        <v>0.382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.118</v>
+        <v>0.313</v>
       </c>
       <c r="S16" t="n">
-        <v>0.074</v>
+        <v>0.238</v>
       </c>
       <c r="T16" t="n">
-        <v>0.046</v>
+        <v>0.144</v>
       </c>
       <c r="U16" t="n">
-        <v>0.012</v>
+        <v>0.05</v>
       </c>
       <c r="V16" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inputxgradient_u2net_fill</t>
+          <t>U2Net-Saliency</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0.86</v>
       </c>
       <c r="C17" t="n">
-        <v>0.821</v>
+        <v>0.83</v>
       </c>
       <c r="D17" t="n">
-        <v>0.801</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.794</v>
+        <v>0.792</v>
       </c>
       <c r="F17" t="n">
-        <v>0.767</v>
+        <v>0.783</v>
       </c>
       <c r="G17" t="n">
-        <v>0.748</v>
+        <v>0.774</v>
       </c>
       <c r="H17" t="n">
-        <v>0.721</v>
+        <v>0.762</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="J17" t="n">
-        <v>0.659</v>
+        <v>0.717</v>
       </c>
       <c r="K17" t="n">
-        <v>0.635</v>
+        <v>0.707</v>
       </c>
       <c r="L17" t="n">
-        <v>0.608</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.573</v>
+        <v>0.643</v>
       </c>
       <c r="N17" t="n">
-        <v>0.544</v>
+        <v>0.618</v>
       </c>
       <c r="O17" t="n">
-        <v>0.51</v>
+        <v>0.549</v>
       </c>
       <c r="P17" t="n">
-        <v>0.466</v>
+        <v>0.487</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.42</v>
+        <v>0.404</v>
       </c>
       <c r="R17" t="n">
-        <v>0.348</v>
+        <v>0.342</v>
       </c>
       <c r="S17" t="n">
-        <v>0.263</v>
+        <v>0.233</v>
       </c>
       <c r="T17" t="n">
-        <v>0.165</v>
+        <v>0.134</v>
       </c>
       <c r="U17" t="n">
-        <v>0.061</v>
+        <v>0.054</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2515,494 +2355,156 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>inputxgradient_u2net_fill</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0.86</v>
       </c>
       <c r="C18" t="n">
-        <v>0.783</v>
+        <v>0.821</v>
       </c>
       <c r="D18" t="n">
-        <v>0.734</v>
+        <v>0.801</v>
       </c>
       <c r="E18" t="n">
-        <v>0.705</v>
+        <v>0.794</v>
       </c>
       <c r="F18" t="n">
-        <v>0.657</v>
+        <v>0.767</v>
       </c>
       <c r="G18" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="K18" t="n">
         <v>0.635</v>
       </c>
-      <c r="H18" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.463</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.434</v>
+        <v>0.608</v>
       </c>
       <c r="M18" t="n">
-        <v>0.373</v>
+        <v>0.573</v>
       </c>
       <c r="N18" t="n">
-        <v>0.318</v>
+        <v>0.544</v>
       </c>
       <c r="O18" t="n">
-        <v>0.286</v>
+        <v>0.51</v>
       </c>
       <c r="P18" t="n">
-        <v>0.231</v>
+        <v>0.466</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.186</v>
+        <v>0.42</v>
       </c>
       <c r="R18" t="n">
-        <v>0.129</v>
+        <v>0.348</v>
       </c>
       <c r="S18" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.263</v>
       </c>
       <c r="T18" t="n">
-        <v>0.046</v>
+        <v>0.165</v>
       </c>
       <c r="U18" t="n">
-        <v>0.012</v>
+        <v>0.061</v>
       </c>
       <c r="V18" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>dinov2_COMBO_ENT_SMOOTH</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0.86</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.851</v>
       </c>
       <c r="D19" t="n">
-        <v>0.771</v>
+        <v>0.843</v>
       </c>
       <c r="E19" t="n">
-        <v>0.724</v>
+        <v>0.832</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="G19" t="n">
-        <v>0.641</v>
+        <v>0.806</v>
       </c>
       <c r="H19" t="n">
-        <v>0.612</v>
+        <v>0.795</v>
       </c>
       <c r="I19" t="n">
-        <v>0.547</v>
+        <v>0.78</v>
       </c>
       <c r="J19" t="n">
-        <v>0.509</v>
+        <v>0.764</v>
       </c>
       <c r="K19" t="n">
-        <v>0.455</v>
+        <v>0.737</v>
       </c>
       <c r="L19" t="n">
-        <v>0.417</v>
+        <v>0.713</v>
       </c>
       <c r="M19" t="n">
-        <v>0.366</v>
+        <v>0.681</v>
       </c>
       <c r="N19" t="n">
-        <v>0.331</v>
+        <v>0.636</v>
       </c>
       <c r="O19" t="n">
-        <v>0.298</v>
+        <v>0.581</v>
       </c>
       <c r="P19" t="n">
-        <v>0.263</v>
+        <v>0.544</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.217</v>
+        <v>0.47</v>
       </c>
       <c r="R19" t="n">
-        <v>0.161</v>
+        <v>0.398</v>
       </c>
       <c r="S19" t="n">
-        <v>0.139</v>
+        <v>0.306</v>
       </c>
       <c r="T19" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.204</v>
       </c>
       <c r="U19" t="n">
-        <v>0.026</v>
+        <v>0.094</v>
       </c>
       <c r="V19" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>random_baseline</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>saliency</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.671</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>sumDino</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.831</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.8169999999999999</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.721</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.494</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>u2net_dino_fusion</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.834</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.801</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.718</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.307</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>xrai</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.841</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="V24" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:V19">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/results/excel_reports/vgg16_resnet50_random_noise.xlsx
+++ b/results/excel_reports/vgg16_resnet50_random_noise.xlsx
@@ -560,198 +560,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="12"/>
-          <order val="12"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$14:$V$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="13"/>
-          <order val="13"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A15</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$15:$V$15</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="14"/>
-          <order val="14"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A16</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$16:$V$16</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="15"/>
-          <order val="15"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A17</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$17:$V$17</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="16"/>
-          <order val="16"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A18</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$18:$V$18</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="17"/>
-          <order val="17"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A19</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$19:$V$19</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -825,7 +633,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1135,7 +943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1235,342 +1043,342 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0.86</v>
       </c>
       <c r="C2" t="n">
-        <v>0.618</v>
+        <v>0.786</v>
       </c>
       <c r="D2" t="n">
-        <v>0.545</v>
+        <v>0.728</v>
       </c>
       <c r="E2" t="n">
-        <v>0.459</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.398</v>
+        <v>0.636</v>
       </c>
       <c r="G2" t="n">
-        <v>0.328</v>
+        <v>0.598</v>
       </c>
       <c r="H2" t="n">
-        <v>0.273</v>
+        <v>0.551</v>
       </c>
       <c r="I2" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="J2" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="P2" t="n">
         <v>0.169</v>
       </c>
-      <c r="K2" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.027</v>
-      </c>
       <c r="Q2" t="n">
-        <v>0.017</v>
+        <v>0.121</v>
       </c>
       <c r="R2" t="n">
-        <v>0.008</v>
+        <v>0.089</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003</v>
+        <v>0.049</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003</v>
+        <v>0.023</v>
       </c>
       <c r="U2" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="V2" t="n">
         <v>0.002</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.86</v>
       </c>
       <c r="C3" t="n">
-        <v>0.743</v>
+        <v>0.788</v>
       </c>
       <c r="D3" t="n">
-        <v>0.671</v>
+        <v>0.749</v>
       </c>
       <c r="E3" t="n">
-        <v>0.618</v>
+        <v>0.657</v>
       </c>
       <c r="F3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.574</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.521</v>
-      </c>
       <c r="H3" t="n">
-        <v>0.488</v>
+        <v>0.543</v>
       </c>
       <c r="I3" t="n">
-        <v>0.43</v>
+        <v>0.504</v>
       </c>
       <c r="J3" t="n">
-        <v>0.386</v>
+        <v>0.451</v>
       </c>
       <c r="K3" t="n">
-        <v>0.355</v>
+        <v>0.397</v>
       </c>
       <c r="L3" t="n">
-        <v>0.309</v>
+        <v>0.347</v>
       </c>
       <c r="M3" t="n">
-        <v>0.266</v>
+        <v>0.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.227</v>
+        <v>0.264</v>
       </c>
       <c r="O3" t="n">
-        <v>0.194</v>
+        <v>0.234</v>
       </c>
       <c r="P3" t="n">
-        <v>0.131</v>
+        <v>0.195</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.095</v>
+        <v>0.148</v>
       </c>
       <c r="R3" t="n">
-        <v>0.064</v>
+        <v>0.114</v>
       </c>
       <c r="S3" t="n">
-        <v>0.03</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.016</v>
+        <v>0.04</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003</v>
+        <v>0.017</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>inputxgradient_continuous</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.86</v>
       </c>
       <c r="C4" t="n">
-        <v>0.786</v>
+        <v>0.837</v>
       </c>
       <c r="D4" t="n">
-        <v>0.728</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.784</v>
       </c>
       <c r="F4" t="n">
-        <v>0.636</v>
+        <v>0.754</v>
       </c>
       <c r="G4" t="n">
-        <v>0.598</v>
+        <v>0.726</v>
       </c>
       <c r="H4" t="n">
-        <v>0.551</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.51</v>
+        <v>0.627</v>
       </c>
       <c r="J4" t="n">
-        <v>0.457</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.414</v>
+        <v>0.507</v>
       </c>
       <c r="L4" t="n">
-        <v>0.377</v>
+        <v>0.462</v>
       </c>
       <c r="M4" t="n">
-        <v>0.325</v>
+        <v>0.394</v>
       </c>
       <c r="N4" t="n">
-        <v>0.267</v>
+        <v>0.337</v>
       </c>
       <c r="O4" t="n">
-        <v>0.223</v>
+        <v>0.279</v>
       </c>
       <c r="P4" t="n">
-        <v>0.169</v>
+        <v>0.222</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.121</v>
+        <v>0.163</v>
       </c>
       <c r="R4" t="n">
-        <v>0.089</v>
+        <v>0.118</v>
       </c>
       <c r="S4" t="n">
-        <v>0.049</v>
+        <v>0.074</v>
       </c>
       <c r="T4" t="n">
-        <v>0.023</v>
+        <v>0.046</v>
       </c>
       <c r="U4" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.86</v>
       </c>
       <c r="C5" t="n">
-        <v>0.788</v>
+        <v>0.786</v>
       </c>
       <c r="D5" t="n">
-        <v>0.749</v>
+        <v>0.739</v>
       </c>
       <c r="E5" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.657</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.62</v>
-      </c>
       <c r="G5" t="n">
-        <v>0.574</v>
+        <v>0.629</v>
       </c>
       <c r="H5" t="n">
-        <v>0.543</v>
+        <v>0.599</v>
       </c>
       <c r="I5" t="n">
-        <v>0.504</v>
+        <v>0.556</v>
       </c>
       <c r="J5" t="n">
-        <v>0.451</v>
+        <v>0.496</v>
       </c>
       <c r="K5" t="n">
-        <v>0.397</v>
+        <v>0.467</v>
       </c>
       <c r="L5" t="n">
-        <v>0.347</v>
+        <v>0.422</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3</v>
+        <v>0.368</v>
       </c>
       <c r="N5" t="n">
-        <v>0.264</v>
+        <v>0.333</v>
       </c>
       <c r="O5" t="n">
-        <v>0.234</v>
+        <v>0.266</v>
       </c>
       <c r="P5" t="n">
-        <v>0.195</v>
+        <v>0.233</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.148</v>
+        <v>0.186</v>
       </c>
       <c r="R5" t="n">
-        <v>0.114</v>
+        <v>0.122</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="U5" t="n">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inputxgradient_continuous</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.86</v>
       </c>
       <c r="C6" t="n">
-        <v>0.837</v>
+        <v>0.783</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.734</v>
       </c>
       <c r="E6" t="n">
-        <v>0.784</v>
+        <v>0.705</v>
       </c>
       <c r="F6" t="n">
-        <v>0.754</v>
+        <v>0.657</v>
       </c>
       <c r="G6" t="n">
-        <v>0.726</v>
+        <v>0.635</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.591</v>
       </c>
       <c r="I6" t="n">
-        <v>0.627</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.516</v>
       </c>
       <c r="K6" t="n">
-        <v>0.507</v>
+        <v>0.463</v>
       </c>
       <c r="L6" t="n">
-        <v>0.462</v>
+        <v>0.434</v>
       </c>
       <c r="M6" t="n">
-        <v>0.394</v>
+        <v>0.373</v>
       </c>
       <c r="N6" t="n">
-        <v>0.337</v>
+        <v>0.318</v>
       </c>
       <c r="O6" t="n">
-        <v>0.279</v>
+        <v>0.286</v>
       </c>
       <c r="P6" t="n">
-        <v>0.222</v>
+        <v>0.231</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.163</v>
+        <v>0.186</v>
       </c>
       <c r="R6" t="n">
-        <v>0.118</v>
+        <v>0.129</v>
       </c>
       <c r="S6" t="n">
-        <v>0.074</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>0.046</v>
@@ -1579,144 +1387,144 @@
         <v>0.012</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.86</v>
       </c>
       <c r="C7" t="n">
-        <v>0.795</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.751</v>
+        <v>0.771</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.724</v>
       </c>
       <c r="F7" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.641</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.606</v>
-      </c>
       <c r="H7" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.612</v>
       </c>
       <c r="I7" t="n">
-        <v>0.506</v>
+        <v>0.547</v>
       </c>
       <c r="J7" t="n">
-        <v>0.47</v>
+        <v>0.509</v>
       </c>
       <c r="K7" t="n">
-        <v>0.423</v>
+        <v>0.455</v>
       </c>
       <c r="L7" t="n">
-        <v>0.391</v>
+        <v>0.417</v>
       </c>
       <c r="M7" t="n">
-        <v>0.329</v>
+        <v>0.366</v>
       </c>
       <c r="N7" t="n">
-        <v>0.306</v>
+        <v>0.331</v>
       </c>
       <c r="O7" t="n">
-        <v>0.28</v>
+        <v>0.298</v>
       </c>
       <c r="P7" t="n">
-        <v>0.243</v>
+        <v>0.263</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.185</v>
+        <v>0.217</v>
       </c>
       <c r="R7" t="n">
-        <v>0.153</v>
+        <v>0.161</v>
       </c>
       <c r="S7" t="n">
-        <v>0.117</v>
+        <v>0.139</v>
       </c>
       <c r="T7" t="n">
-        <v>0.065</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.022</v>
+        <v>0.026</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>xrai</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.86</v>
       </c>
       <c r="C8" t="n">
-        <v>0.786</v>
+        <v>0.841</v>
       </c>
       <c r="D8" t="n">
-        <v>0.739</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.781</v>
       </c>
       <c r="F8" t="n">
-        <v>0.657</v>
+        <v>0.763</v>
       </c>
       <c r="G8" t="n">
-        <v>0.629</v>
+        <v>0.73</v>
       </c>
       <c r="H8" t="n">
-        <v>0.599</v>
+        <v>0.698</v>
       </c>
       <c r="I8" t="n">
-        <v>0.556</v>
+        <v>0.656</v>
       </c>
       <c r="J8" t="n">
-        <v>0.496</v>
+        <v>0.603</v>
       </c>
       <c r="K8" t="n">
-        <v>0.467</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.422</v>
+        <v>0.504</v>
       </c>
       <c r="M8" t="n">
-        <v>0.368</v>
+        <v>0.455</v>
       </c>
       <c r="N8" t="n">
-        <v>0.333</v>
+        <v>0.398</v>
       </c>
       <c r="O8" t="n">
-        <v>0.266</v>
+        <v>0.35</v>
       </c>
       <c r="P8" t="n">
-        <v>0.233</v>
+        <v>0.293</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.186</v>
+        <v>0.225</v>
       </c>
       <c r="R8" t="n">
-        <v>0.122</v>
+        <v>0.155</v>
       </c>
       <c r="S8" t="n">
-        <v>0.079</v>
+        <v>0.103</v>
       </c>
       <c r="T8" t="n">
-        <v>0.037</v>
+        <v>0.059</v>
       </c>
       <c r="U8" t="n">
-        <v>0.007</v>
+        <v>0.019</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1725,68 +1533,68 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.86</v>
       </c>
       <c r="C9" t="n">
-        <v>0.783</v>
+        <v>0.772</v>
       </c>
       <c r="D9" t="n">
         <v>0.734</v>
       </c>
       <c r="E9" t="n">
-        <v>0.705</v>
+        <v>0.702</v>
       </c>
       <c r="F9" t="n">
-        <v>0.657</v>
+        <v>0.666</v>
       </c>
       <c r="G9" t="n">
-        <v>0.635</v>
+        <v>0.64</v>
       </c>
       <c r="H9" t="n">
-        <v>0.591</v>
+        <v>0.608</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.574</v>
       </c>
       <c r="J9" t="n">
-        <v>0.516</v>
+        <v>0.543</v>
       </c>
       <c r="K9" t="n">
-        <v>0.463</v>
+        <v>0.525</v>
       </c>
       <c r="L9" t="n">
-        <v>0.434</v>
+        <v>0.484</v>
       </c>
       <c r="M9" t="n">
-        <v>0.373</v>
+        <v>0.46</v>
       </c>
       <c r="N9" t="n">
-        <v>0.318</v>
+        <v>0.417</v>
       </c>
       <c r="O9" t="n">
-        <v>0.286</v>
+        <v>0.377</v>
       </c>
       <c r="P9" t="n">
-        <v>0.231</v>
+        <v>0.322</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.186</v>
+        <v>0.288</v>
       </c>
       <c r="R9" t="n">
-        <v>0.129</v>
+        <v>0.229</v>
       </c>
       <c r="S9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.165</v>
       </c>
       <c r="T9" t="n">
-        <v>0.046</v>
+        <v>0.103</v>
       </c>
       <c r="U9" t="n">
-        <v>0.012</v>
+        <v>0.034</v>
       </c>
       <c r="V9" t="n">
         <v>0.002</v>
@@ -1795,68 +1603,68 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.86</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.821</v>
       </c>
       <c r="D10" t="n">
-        <v>0.771</v>
+        <v>0.798</v>
       </c>
       <c r="E10" t="n">
-        <v>0.724</v>
+        <v>0.775</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.756</v>
       </c>
       <c r="G10" t="n">
-        <v>0.641</v>
+        <v>0.732</v>
       </c>
       <c r="H10" t="n">
-        <v>0.612</v>
+        <v>0.705</v>
       </c>
       <c r="I10" t="n">
-        <v>0.547</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.509</v>
+        <v>0.635</v>
       </c>
       <c r="K10" t="n">
-        <v>0.455</v>
+        <v>0.614</v>
       </c>
       <c r="L10" t="n">
-        <v>0.417</v>
+        <v>0.571</v>
       </c>
       <c r="M10" t="n">
-        <v>0.366</v>
+        <v>0.524</v>
       </c>
       <c r="N10" t="n">
-        <v>0.331</v>
+        <v>0.486</v>
       </c>
       <c r="O10" t="n">
-        <v>0.298</v>
+        <v>0.435</v>
       </c>
       <c r="P10" t="n">
-        <v>0.263</v>
+        <v>0.374</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.217</v>
+        <v>0.322</v>
       </c>
       <c r="R10" t="n">
-        <v>0.161</v>
+        <v>0.258</v>
       </c>
       <c r="S10" t="n">
-        <v>0.139</v>
+        <v>0.186</v>
       </c>
       <c r="T10" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="U10" t="n">
-        <v>0.026</v>
+        <v>0.049</v>
       </c>
       <c r="V10" t="n">
         <v>0.001</v>
@@ -1865,147 +1673,147 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>xrai</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.86</v>
       </c>
       <c r="C11" t="n">
-        <v>0.841</v>
+        <v>0.833</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="E11" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.781</v>
       </c>
-      <c r="F11" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.73</v>
-      </c>
       <c r="H11" t="n">
-        <v>0.698</v>
+        <v>0.768</v>
       </c>
       <c r="I11" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.656</v>
       </c>
-      <c r="J11" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.5580000000000001</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.504</v>
+        <v>0.615</v>
       </c>
       <c r="M11" t="n">
-        <v>0.455</v>
+        <v>0.576</v>
       </c>
       <c r="N11" t="n">
-        <v>0.398</v>
+        <v>0.521</v>
       </c>
       <c r="O11" t="n">
-        <v>0.35</v>
+        <v>0.465</v>
       </c>
       <c r="P11" t="n">
-        <v>0.293</v>
+        <v>0.399</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.225</v>
+        <v>0.326</v>
       </c>
       <c r="R11" t="n">
-        <v>0.155</v>
+        <v>0.243</v>
       </c>
       <c r="S11" t="n">
-        <v>0.103</v>
+        <v>0.142</v>
       </c>
       <c r="T11" t="n">
-        <v>0.059</v>
+        <v>0.063</v>
       </c>
       <c r="U11" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.86</v>
       </c>
       <c r="C12" t="n">
-        <v>0.772</v>
+        <v>0.836</v>
       </c>
       <c r="D12" t="n">
-        <v>0.734</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.702</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F12" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="K12" t="n">
         <v>0.666</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.543</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.525</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.484</v>
+        <v>0.633</v>
       </c>
       <c r="M12" t="n">
-        <v>0.46</v>
+        <v>0.585</v>
       </c>
       <c r="N12" t="n">
-        <v>0.417</v>
+        <v>0.533</v>
       </c>
       <c r="O12" t="n">
-        <v>0.377</v>
+        <v>0.488</v>
       </c>
       <c r="P12" t="n">
-        <v>0.322</v>
+        <v>0.414</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.288</v>
+        <v>0.338</v>
       </c>
       <c r="R12" t="n">
-        <v>0.229</v>
+        <v>0.274</v>
       </c>
       <c r="S12" t="n">
-        <v>0.165</v>
+        <v>0.187</v>
       </c>
       <c r="T12" t="n">
-        <v>0.103</v>
+        <v>0.098</v>
       </c>
       <c r="U12" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="V12" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>inputxgradient_u2net_fill</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2015,485 +1823,65 @@
         <v>0.821</v>
       </c>
       <c r="D13" t="n">
-        <v>0.798</v>
+        <v>0.801</v>
       </c>
       <c r="E13" t="n">
-        <v>0.775</v>
+        <v>0.794</v>
       </c>
       <c r="F13" t="n">
-        <v>0.756</v>
+        <v>0.767</v>
       </c>
       <c r="G13" t="n">
-        <v>0.732</v>
+        <v>0.748</v>
       </c>
       <c r="H13" t="n">
-        <v>0.705</v>
+        <v>0.721</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="J13" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.635</v>
       </c>
-      <c r="K13" t="n">
-        <v>0.614</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.571</v>
+        <v>0.608</v>
       </c>
       <c r="M13" t="n">
-        <v>0.524</v>
+        <v>0.573</v>
       </c>
       <c r="N13" t="n">
-        <v>0.486</v>
+        <v>0.544</v>
       </c>
       <c r="O13" t="n">
-        <v>0.435</v>
+        <v>0.51</v>
       </c>
       <c r="P13" t="n">
-        <v>0.374</v>
+        <v>0.466</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.322</v>
+        <v>0.42</v>
       </c>
       <c r="R13" t="n">
-        <v>0.258</v>
+        <v>0.348</v>
       </c>
       <c r="S13" t="n">
-        <v>0.186</v>
+        <v>0.263</v>
       </c>
       <c r="T13" t="n">
-        <v>0.12</v>
+        <v>0.165</v>
       </c>
       <c r="U13" t="n">
-        <v>0.049</v>
+        <v>0.061</v>
       </c>
       <c r="V13" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dinov2_PC1</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.789</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dinov2_COMBO_FIXED</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.782</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.699</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>u2net_dino_fusion</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.843</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.796</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.771</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.648</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.616</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>U2Net-Saliency</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.8090000000000001</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.741</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.717</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.707</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.404</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>inputxgradient_u2net_fill</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.821</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.801</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.748</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.721</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.6929999999999999</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.544</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.466</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>dinov2_COMBO_ENT_SMOOTH</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.851</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.843</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.832</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.737</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.713</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.544</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="V19" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:V19">
+  <conditionalFormatting sqref="B2:V13">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/results/excel_reports/vgg16_resnet50_random_noise.xlsx
+++ b/results/excel_reports/vgg16_resnet50_random_noise.xlsx
@@ -1072,7 +1072,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.92</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C2" t="n">
         <v>0.871</v>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.92</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C3" t="n">
         <v>0.896</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.92</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C4" t="n">
         <v>0.894</v>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.92</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C5" t="n">
         <v>0.89</v>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.92</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C6" t="n">
         <v>0.903</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.92</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C7" t="n">
         <v>0.913</v>
@@ -1613,7 +1613,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.99</v>
+        <v>0.98998998998999</v>
       </c>
       <c r="C2" t="n">
         <v>0.97</v>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.99</v>
+        <v>0.98998998998999</v>
       </c>
       <c r="C3" t="n">
         <v>0.979</v>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.99</v>
+        <v>0.98998998998999</v>
       </c>
       <c r="C4" t="n">
         <v>0.982</v>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.99</v>
+        <v>0.98998998998999</v>
       </c>
       <c r="C5" t="n">
         <v>0.984</v>
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.99</v>
+        <v>0.98998998998999</v>
       </c>
       <c r="C6" t="n">
         <v>0.985</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.99</v>
+        <v>0.98998998998999</v>
       </c>
       <c r="C7" t="n">
         <v>0.987</v>
